--- a/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity non-carcinogenic results.xlsx
@@ -2717,7 +2717,7 @@
         <v>2.224578589058401e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>1.936739618879213e-09</v>
+        <v>1.936739618879212e-09</v>
       </c>
       <c r="P9" t="n">
         <v>2.142695560457661e-09</v>
@@ -2832,7 +2832,7 @@
         <v>5.439685332502717e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>3.44784593728335e-09</v>
+        <v>3.447845937283349e-09</v>
       </c>
       <c r="Y10" t="n">
         <v>7.23164965866645e-09</v>
@@ -2854,16 +2854,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="C11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="D11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="E11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="F11" t="n">
         <v>3.780422291421149e-09</v>
@@ -2872,16 +2872,16 @@
         <v>3.780422291421149e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="J11" t="n">
         <v>3.693989463487269e-09</v>
       </c>
       <c r="K11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="L11" t="n">
         <v>3.780422291421144e-09</v>
@@ -2890,25 +2890,25 @@
         <v>3.780422291421149e-09</v>
       </c>
       <c r="N11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="O11" t="n">
         <v>3.780422291421149e-09</v>
       </c>
       <c r="P11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="Q11" t="n">
         <v>3.780422291421149e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="S11" t="n">
         <v>3.778963157327011e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="U11" t="n">
         <v>3.780422291421149e-09</v>
@@ -2923,13 +2923,13 @@
         <v>3.780422291421149e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="Z11" t="n">
         <v>3.780422291421149e-09</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.780422291421143e-09</v>
+        <v>3.780422291421144e-09</v>
       </c>
       <c r="AB11" t="n">
         <v>3.780422291421149e-09</v>
@@ -3108,7 +3108,7 @@
         <v>5.681064620423241e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.606518477902619e-09</v>
+        <v>6.60651847790262e-09</v>
       </c>
     </row>
     <row r="14">
@@ -3242,7 +3242,7 @@
         <v>1.831633692935754e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>1.600010761570408e-09</v>
+        <v>1.600010761570407e-09</v>
       </c>
       <c r="O15" t="n">
         <v>1.358780907567338e-09</v>
@@ -3336,7 +3336,7 @@
         <v>2.58235901015845e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>2.536097098367212e-09</v>
+        <v>2.536097098367211e-09</v>
       </c>
       <c r="Q16" t="n">
         <v>2.120078258660222e-09</v>
@@ -3360,7 +3360,7 @@
         <v>3.080567818543808e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>2.1015280960274e-09</v>
+        <v>2.101528096027399e-09</v>
       </c>
       <c r="Y16" t="n">
         <v>4.06111354042628e-09</v>
@@ -5014,85 +5014,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.226302964049374e-09</v>
+        <v>6.226302964049157e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.757862160480923e-09</v>
+        <v>1.757862160480926e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.947237991568664e-09</v>
+        <v>5.947237991568459e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.539288178647311e-09</v>
+        <v>2.539288178647304e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>3.22912737301767e-09</v>
+        <v>3.229127373017665e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.978936671782271e-09</v>
+        <v>8.978936671782022e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.044580432276803e-09</v>
+        <v>2.044580432276629e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>3.756069689392092e-09</v>
+        <v>3.756069689391882e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.283547119220372e-09</v>
+        <v>7.283547119220126e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>4.215409381482761e-09</v>
+        <v>4.215409381482548e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.052433142047908e-08</v>
+        <v>1.052433142047884e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.481167145550456e-08</v>
+        <v>1.481167145550454e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.670554866402872e-09</v>
+        <v>2.670554866402685e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>4.03352295072675e-09</v>
+        <v>4.033522950726592e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.967380835530529e-09</v>
+        <v>6.967380835530363e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.226377864920111e-09</v>
+        <v>3.226377864919928e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.029499456038862e-09</v>
+        <v>2.02949945603868e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.124663641543341e-09</v>
+        <v>7.124663641543156e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>3.053290896124633e-09</v>
+        <v>3.053290896124432e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.075355457996067e-08</v>
+        <v>1.075355457996033e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>3.991231717893493e-09</v>
+        <v>3.991231717893508e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.270079264909695e-09</v>
+        <v>4.270079264909497e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>8.288695974667469e-09</v>
+        <v>8.288695974667258e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.043345257998468e-08</v>
+        <v>1.04334525799845e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.671500189698149e-09</v>
+        <v>4.671500189697965e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.798499526563431e-09</v>
+        <v>3.79849952656322e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.266713472739194e-08</v>
+        <v>2.266713472739192e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.394688471808835e-09</v>
+        <v>3.394688471808594e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.140951226380296e-09</v>
+        <v>5.140951226380301e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.113124404898218e-09</v>
+        <v>4.113124404898221e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.63160560836418e-09</v>
+        <v>3.631605608364179e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.450271360956906e-09</v>
+        <v>5.450271360956946e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.063545455745274e-09</v>
+        <v>5.063545455745183e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.083906198884436e-09</v>
+        <v>5.083906198884441e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.777477029365812e-09</v>
+        <v>3.777477029365688e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.14015849059358e-09</v>
+        <v>4.140158490593555e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.05125650082004e-09</v>
+        <v>4.051256500820088e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.060098854435777e-09</v>
+        <v>3.060098854435498e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.266217975804496e-09</v>
+        <v>4.266217975804382e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.548224848314421e-09</v>
+        <v>4.548224848314425e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.097571461090309e-09</v>
+        <v>5.097571461090117e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.216140797497728e-09</v>
+        <v>3.216140797497544e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.789994516805678e-09</v>
+        <v>6.789994516805628e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.363062761361844e-09</v>
+        <v>3.363062761361788e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.097236861305396e-09</v>
+        <v>5.097236861305426e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.922406271250943e-09</v>
+        <v>6.922406271250945e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.152471172867757e-09</v>
+        <v>6.152471172867502e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.551557963373172e-09</v>
+        <v>4.551557963373111e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>6.050755267344865e-09</v>
+        <v>6.050755267344639e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.759310045440928e-09</v>
+        <v>4.759310045440897e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>5.042038169169911e-09</v>
+        <v>5.042038169169837e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.155773836279479e-09</v>
+        <v>7.155773836279209e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.628282414301758e-09</v>
+        <v>4.628282414301547e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>5.252100151198796e-09</v>
+        <v>5.25210015119855e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.379510645151329e-09</v>
+        <v>6.379510645151153e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>5.419524075126856e-09</v>
+        <v>5.419524075126603e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.719052075238153e-09</v>
+        <v>7.719052075237842e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>9.273265381011379e-09</v>
+        <v>9.273265381011189e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.856442744977833e-09</v>
+        <v>4.856442744977588e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.353228606934622e-09</v>
+        <v>5.353228606934359e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.422585354846932e-09</v>
+        <v>6.42258535484663e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.05903370113415e-09</v>
+        <v>5.059033701133921e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.62278557555287e-09</v>
+        <v>4.622785575552577e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.479913090730643e-09</v>
+        <v>6.479913090730347e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.995945533498007e-09</v>
+        <v>4.995945533497784e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.802601225195042e-09</v>
+        <v>7.802601225194724e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>4.371276528863617e-09</v>
+        <v>4.371276528863662e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.439450605669764e-09</v>
+        <v>5.439450605669529e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>6.904189207396597e-09</v>
+        <v>6.904189207396413e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.685927805031141e-09</v>
+        <v>7.685927805030873e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.585763819032724e-09</v>
+        <v>5.585763819032412e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.267565328611486e-09</v>
+        <v>5.267565328611191e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.217464938388441e-08</v>
+        <v>1.21746493838842e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.120380940942187e-09</v>
+        <v>5.120380940941945e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.784654201655983e-09</v>
+        <v>5.78465420165592e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.332954868991385e-09</v>
+        <v>5.332954868991343e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.188736759815718e-09</v>
+        <v>5.188736759815581e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.869616766163649e-09</v>
+        <v>5.869616766163627e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.570346107390077e-09</v>
+        <v>5.570346107390175e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.72760917416011e-09</v>
+        <v>5.727609174160009e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.259902875241604e-09</v>
+        <v>5.259902875241329e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.392096009038361e-09</v>
+        <v>5.392096009038173e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.359692277705884e-09</v>
+        <v>5.359692277705563e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.998426954359187e-09</v>
+        <v>4.998426954359047e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.438043211132389e-09</v>
+        <v>5.438043211132345e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.5742939843585e-09</v>
+        <v>4.574293984358956e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.741061794273608e-09</v>
+        <v>5.741061794273433e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.055302410268545e-09</v>
+        <v>5.055302410268214e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.357930124646825e-09</v>
+        <v>6.357930124646784e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.108853740852223e-09</v>
+        <v>5.108853740851922e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.740939836581066e-09</v>
+        <v>5.74093983658098e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.43588074555677e-09</v>
+        <v>6.435880745556776e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.840708829148578e-09</v>
+        <v>2.840708829148439e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.239795619653965e-09</v>
+        <v>1.239795619653966e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.738992923625729e-09</v>
+        <v>2.73899292362559e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.447547701721789e-09</v>
+        <v>1.447547701721788e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.730275825450728e-09</v>
+        <v>1.730275825450727e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.72720257086667e-09</v>
+        <v>3.727202570866388e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.316520070582606e-09</v>
+        <v>1.31652007058249e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.940337807479613e-09</v>
+        <v>1.940337807479481e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.091958011808466e-09</v>
+        <v>3.091958011808413e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.107761731407659e-09</v>
+        <v>2.107761731407563e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.407289731518957e-09</v>
+        <v>4.407289731518808e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.961503037292104e-09</v>
+        <v>5.961503037292091e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.544680401258626e-09</v>
+        <v>1.544680401258535e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.924657341521661e-09</v>
+        <v>1.924657341521502e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.994014089433983e-09</v>
+        <v>2.994014089433877e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.747271357415001e-09</v>
+        <v>1.747271357414872e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.311023231833638e-09</v>
+        <v>1.311023231833513e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.168150747011467e-09</v>
+        <v>3.168150747011326e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.684183189778839e-09</v>
+        <v>1.684183189778741e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.374029959782023e-09</v>
+        <v>4.374029959781879e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.86188247516505e-09</v>
+        <v>1.861882475165103e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.010879340256858e-09</v>
+        <v>2.010879340256725e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>3.4756179419837e-09</v>
+        <v>3.475617941983534e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.374165461311957e-09</v>
+        <v>4.374165461311818e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.274001475313514e-09</v>
+        <v>2.274001475313378e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.955802984892249e-09</v>
+        <v>1.955802984892128e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.862887040165101e-09</v>
+        <v>8.8628870401651e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.808618597223005e-09</v>
+        <v>1.808618597222868e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.472891857936777e-09</v>
+        <v>2.472891857936782e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.021192525272214e-09</v>
+        <v>2.021192525272212e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.876974416096481e-09</v>
+        <v>1.87697441609648e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.44104550075069e-09</v>
+        <v>2.441045500750793e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.282793474047614e-09</v>
+        <v>2.282793474047415e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.415846830440901e-09</v>
+        <v>2.4158468304409e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.948140531522384e-09</v>
+        <v>1.948140531522152e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.963524743625482e-09</v>
+        <v>1.96352474362533e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.931121012292947e-09</v>
+        <v>1.93112101229276e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.686664610640005e-09</v>
+        <v>1.686664610640042e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.009471945719494e-09</v>
+        <v>2.009471945719489e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.064899930659924e-09</v>
+        <v>2.064899930659981e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.312490528860662e-09</v>
+        <v>2.312490528860642e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.626731144855646e-09</v>
+        <v>1.626731144855423e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.046167780927601e-09</v>
+        <v>3.046167780927775e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.797091397133008e-09</v>
+        <v>1.797091397132772e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.42917749286187e-09</v>
+        <v>2.429177492861852e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.124118401837648e-09</v>
+        <v>3.124118401837647e-09</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>2.054176268332245e-09</v>
+        <v>2.054176268332249e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.014692762481472e-09</v>
+        <v>2.014692762481475e-09</v>
       </c>
     </row>
     <row r="9">
@@ -5630,40 +5630,40 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.793411931575797e-09</v>
+        <v>6.793411931575783e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>1.944185281184667e-09</v>
+        <v>1.94418528118467e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>6.493499971289433e-09</v>
+        <v>6.493499971289443e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>2.914315418838139e-09</v>
+        <v>2.914315418838138e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>3.602773956256776e-09</v>
+        <v>3.602773956256772e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>9.751675607227918e-09</v>
+        <v>9.751675607227947e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>2.299302223972298e-09</v>
+        <v>2.299302223972307e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.138644845683869e-09</v>
+        <v>4.138644845683868e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>7.965843640423221e-09</v>
+        <v>7.965843640423287e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>4.632298586128776e-09</v>
+        <v>4.632298586128778e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>1.141251596414518e-08</v>
+        <v>1.141251596414515e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>1.603445962103533e-08</v>
+        <v>1.603445962103531e-08</v>
       </c>
       <c r="N9" t="n">
         <v>2.972038819894905e-09</v>
@@ -5672,43 +5672,43 @@
         <v>4.436824695182837e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>7.589850535765519e-09</v>
+        <v>7.589850535765525e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.56938345822671e-09</v>
+        <v>3.569383458226704e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>2.283094653719584e-09</v>
+        <v>2.283094653719581e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>7.758882837638898e-09</v>
+        <v>7.758882837638888e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>3.383366375358775e-09</v>
+        <v>3.383366375358768e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.165886277898207e-08</v>
+        <v>1.165886277898211e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>4.481272301512182e-09</v>
+        <v>4.481272301512208e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.691052473302256e-09</v>
+        <v>4.69105247330224e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>9.009871866325123e-09</v>
+        <v>9.009871866325121e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.131484820255207e-08</v>
+        <v>1.131484820255205e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>5.122460741359261e-09</v>
+        <v>5.122460741359254e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.184244318550608e-09</v>
+        <v>4.184244318550593e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.441221796208949e-08</v>
+        <v>2.441221796208947e-08</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.750267370672854e-09</v>
+        <v>3.750267370672852e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>4.605721916718375e-09</v>
+        <v>4.605721916718372e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>4.035318519131723e-09</v>
+        <v>4.035318519131726e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>5.959408447517409e-09</v>
+        <v>5.959408447517408e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>5.580001215222997e-09</v>
+        <v>5.580001215223e-09</v>
       </c>
       <c r="N10" t="n">
-        <v>4.16165137795842e-09</v>
+        <v>4.161651377958422e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>4.551426228701789e-09</v>
+        <v>4.551426228701785e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>4.455882994488947e-09</v>
+        <v>4.455882994488954e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.390682908510467e-09</v>
+        <v>3.39068290851047e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>4.686902734356357e-09</v>
+        <v>4.68690273435636e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>5.079874484099396e-09</v>
+        <v>5.079874484099397e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>5.580360810612029e-09</v>
+        <v>5.580360810612031e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>3.55838165126064e-09</v>
+        <v>3.558381651260641e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.399212928674202e-09</v>
+        <v>7.399212928674203e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.716279125099632e-09</v>
+        <v>3.716279125099633e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.580001215222956e-09</v>
+        <v>5.580001215222964e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.491311215957071e-09</v>
+        <v>7.491311215957072e-09</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="C11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="D11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="E11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="F11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>4.263345332908908e-09</v>
+        <v>4.263345332908756e-09</v>
       </c>
       <c r="K11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="L11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="N11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="O11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="P11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>4.400471113093219e-09</v>
+        <v>4.400471113093094e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="U11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="V11" t="n">
-        <v>3.595675830800815e-09</v>
+        <v>3.595675830800573e-09</v>
       </c>
       <c r="W11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="X11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.381063965757433e-09</v>
+        <v>4.381063965757306e-09</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.729925977686281e-09</v>
+        <v>6.729925977686169e-09</v>
       </c>
       <c r="C12" t="n">
-        <v>4.346407745436795e-09</v>
+        <v>4.346407745436675e-09</v>
       </c>
       <c r="D12" t="n">
-        <v>6.58251162134655e-09</v>
+        <v>6.58251162134651e-09</v>
       </c>
       <c r="E12" t="n">
-        <v>4.823251382053605e-09</v>
+        <v>4.823251382053468e-09</v>
       </c>
       <c r="F12" t="n">
-        <v>5.161646263215222e-09</v>
+        <v>5.161646263215179e-09</v>
       </c>
       <c r="G12" t="n">
-        <v>8.18398781374199e-09</v>
+        <v>8.183987813741882e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>4.520956754740526e-09</v>
+        <v>4.520956754740367e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>5.425040434526742e-09</v>
+        <v>5.425040434526622e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>7.188487348965692e-09</v>
+        <v>7.188487348965564e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>5.667683803376841e-09</v>
+        <v>5.667683803376746e-09</v>
       </c>
       <c r="L12" t="n">
-        <v>9.000333090415829e-09</v>
+        <v>9.000333090415762e-09</v>
       </c>
       <c r="M12" t="n">
-        <v>1.127213595072121e-08</v>
+        <v>1.127213595072104e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>4.85162390179035e-09</v>
+        <v>4.851623901790261e-09</v>
       </c>
       <c r="O12" t="n">
-        <v>5.571603414360427e-09</v>
+        <v>5.571603414360297e-09</v>
       </c>
       <c r="P12" t="n">
-        <v>7.121395807994243e-09</v>
+        <v>7.121395807994102e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.145233984190854e-09</v>
+        <v>5.145233984190813e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>4.512990321743494e-09</v>
+        <v>4.51299032174336e-09</v>
       </c>
       <c r="S12" t="n">
-        <v>7.204479483475125e-09</v>
+        <v>7.204479483475009e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>5.05380185686615e-09</v>
+        <v>5.05380185686597e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>9.121418815409343e-09</v>
+        <v>9.121418815409322e-09</v>
       </c>
       <c r="V12" t="n">
-        <v>4.808062408379903e-09</v>
+        <v>4.808062408380033e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>5.69656283324901e-09</v>
+        <v>5.696562833248882e-09</v>
       </c>
       <c r="X12" t="n">
-        <v>7.819372408304069e-09</v>
+        <v>7.819372408303955e-09</v>
       </c>
       <c r="Y12" t="n">
-        <v>8.952326901544227e-09</v>
+        <v>8.952326901544106e-09</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.908610969290272e-09</v>
+        <v>5.908610969290165e-09</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.447453735202243e-09</v>
+        <v>5.44745373520212e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.539001725240712e-08</v>
+        <v>1.539001725240696e-08</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.234143027698092e-09</v>
+        <v>5.234143027697992e-09</v>
       </c>
       <c r="C13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="D13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="E13" t="n">
-        <v>5.654620694419564e-09</v>
+        <v>5.654620694419539e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>5.374252917059649e-09</v>
+        <v>5.374252917059608e-09</v>
       </c>
       <c r="G13" t="n">
-        <v>6.319992053510381e-09</v>
+        <v>6.319992053510329e-09</v>
       </c>
       <c r="H13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="I13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>6.015785116274492e-09</v>
+        <v>6.015785116274456e-09</v>
       </c>
       <c r="K13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="L13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>6.133503749123157e-09</v>
+        <v>6.133503749122985e-09</v>
       </c>
       <c r="N13" t="n">
-        <v>5.436348730279966e-09</v>
+        <v>5.43634873027988e-09</v>
       </c>
       <c r="O13" t="n">
-        <v>5.627932982821396e-09</v>
+        <v>5.627932982821327e-09</v>
       </c>
       <c r="P13" t="n">
-        <v>5.580971053191655e-09</v>
+        <v>5.580971053191531e-09</v>
       </c>
       <c r="Q13" t="n">
         <v>5.05739811899627e-09</v>
       </c>
       <c r="R13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="S13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="T13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="U13" t="n">
-        <v>5.694523131013966e-09</v>
+        <v>5.694523131013958e-09</v>
       </c>
       <c r="V13" t="n">
-        <v>5.102290605765885e-09</v>
+        <v>5.102290605765675e-09</v>
       </c>
       <c r="W13" t="n">
-        <v>6.133680499402652e-09</v>
+        <v>6.133680499402565e-09</v>
       </c>
       <c r="X13" t="n">
-        <v>5.139826316250858e-09</v>
+        <v>5.139826316250769e-09</v>
       </c>
       <c r="Y13" t="n">
-        <v>7.027692575496684e-09</v>
+        <v>7.027692575496659e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.217436940553322e-09</v>
+        <v>5.217436940553284e-09</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.133503749123149e-09</v>
+        <v>6.133503749122964e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.072961226092759e-09</v>
+        <v>7.072961226092718e-09</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>1.432929484601304e-09</v>
+        <v>1.432929484601306e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>1.436468985431732e-09</v>
+        <v>1.436468985431733e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>1.432929484601304e-09</v>
+        <v>1.432929484601306e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>1.432929484601304e-09</v>
+        <v>1.432929484601306e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>1.552777422894443e-09</v>
+        <v>1.552777422894445e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>1.432929484601304e-09</v>
+        <v>1.432929484601307e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>1.437916646651281e-09</v>
+        <v>1.437916646651282e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.432929484601304e-09</v>
+        <v>1.432929484601306e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.432929484601304e-09</v>
+        <v>1.432929484601306e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.533370275558725e-09</v>
+        <v>1.533370275558728e-09</v>
       </c>
     </row>
     <row r="15">
@@ -6158,85 +6158,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.882232287487487e-09</v>
+        <v>3.882232287487486e-09</v>
       </c>
       <c r="C15" t="n">
-        <v>1.498714055238033e-09</v>
+        <v>1.498714055238037e-09</v>
       </c>
       <c r="D15" t="n">
-        <v>3.734817931147888e-09</v>
+        <v>3.734817931147887e-09</v>
       </c>
       <c r="E15" t="n">
-        <v>1.975557691854857e-09</v>
+        <v>1.975557691854861e-09</v>
       </c>
       <c r="F15" t="n">
-        <v>2.313952573016529e-09</v>
+        <v>2.313952573016527e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>5.235853332585884e-09</v>
+        <v>5.235853332585808e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>1.673263064541758e-09</v>
+        <v>1.673263064541763e-09</v>
       </c>
       <c r="I15" t="n">
-        <v>2.577346744327981e-09</v>
+        <v>2.577346744327983e-09</v>
       </c>
       <c r="J15" t="n">
-        <v>4.361611001488602e-09</v>
+        <v>4.361611001488559e-09</v>
       </c>
       <c r="K15" t="n">
-        <v>2.819990113178086e-09</v>
+        <v>2.819990113178083e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>6.152639400217118e-09</v>
+        <v>6.152639400217102e-09</v>
       </c>
       <c r="M15" t="n">
-        <v>8.424442260522463e-09</v>
+        <v>8.424442260522451e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>2.003930211591619e-09</v>
+        <v>2.003930211591617e-09</v>
       </c>
       <c r="O15" t="n">
-        <v>2.623468933204235e-09</v>
+        <v>2.623468933204243e-09</v>
       </c>
       <c r="P15" t="n">
-        <v>4.173261326838041e-09</v>
+        <v>4.17326132683804e-09</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.297540293992175e-09</v>
+        <v>2.297540293992172e-09</v>
       </c>
       <c r="R15" t="n">
-        <v>1.665296631544719e-09</v>
+        <v>1.665296631544718e-09</v>
       </c>
       <c r="S15" t="n">
-        <v>4.356785793276333e-09</v>
+        <v>4.356785793276327e-09</v>
       </c>
       <c r="T15" t="n">
         <v>2.206108166667333e-09</v>
       </c>
       <c r="U15" t="n">
-        <v>6.173284334253177e-09</v>
+        <v>6.17328433425312e-09</v>
       </c>
       <c r="V15" t="n">
-        <v>2.6503032242304e-09</v>
+        <v>2.650303224230388e-09</v>
       </c>
       <c r="W15" t="n">
-        <v>2.748428352092819e-09</v>
+        <v>2.748428352092818e-09</v>
       </c>
       <c r="X15" t="n">
-        <v>4.871237927147898e-09</v>
+        <v>4.871237927147906e-09</v>
       </c>
       <c r="Y15" t="n">
-        <v>6.104633211345462e-09</v>
+        <v>6.104633211345458e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.060917279091502e-09</v>
+        <v>3.060917279091498e-09</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.599760045003479e-09</v>
+        <v>2.599760045003474e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.254232356220834e-08</v>
+        <v>1.254232356220833e-08</v>
       </c>
     </row>
     <row r="16">
@@ -6246,7 +6246,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.38644933749939e-09</v>
+        <v>2.386449337499393e-09</v>
       </c>
       <c r="C16" t="n">
         <v>3.285810058924389e-09</v>
@@ -6255,10 +6255,10 @@
         <v>3.285810058924389e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>2.806927004220893e-09</v>
+        <v>2.806927004220894e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>2.526559226860941e-09</v>
+        <v>2.526559226860945e-09</v>
       </c>
       <c r="G16" t="n">
         <v>3.371857572354267e-09</v>
@@ -6270,7 +6270,7 @@
         <v>3.285810058924389e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.188908768797398e-09</v>
+        <v>3.188908768797397e-09</v>
       </c>
       <c r="K16" t="n">
         <v>3.285810058924389e-09</v>
@@ -6279,19 +6279,19 @@
         <v>3.285810058924389e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>3.285810058924408e-09</v>
+        <v>3.285810058924411e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.588655040081249e-09</v>
+        <v>2.588655040081253e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>2.679798501665248e-09</v>
+        <v>2.679798501665249e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>2.6328365720355e-09</v>
+        <v>2.632836572035503e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.209704428797606e-09</v>
+        <v>2.209704428797605e-09</v>
       </c>
       <c r="R16" t="n">
         <v>3.285810058924389e-09</v>
@@ -6306,25 +6306,25 @@
         <v>2.746388649857865e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>2.94453142161644e-09</v>
+        <v>2.944531421616438e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>3.185546018246524e-09</v>
+        <v>3.185546018246523e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>2.19169183509471e-09</v>
+        <v>2.191691835094713e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.179998885297982e-09</v>
+        <v>4.179998885297983e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.369743250354669e-09</v>
+        <v>2.369743250354672e-09</v>
       </c>
       <c r="AA16" t="n">
         <v>3.285810058924389e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.225267535894046e-09</v>
+        <v>4.225267535894048e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.521141322507439e-09</v>
+        <v>5.521141322507411e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.824591362160234e-09</v>
+        <v>1.824591362160229e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.062572920160344e-09</v>
+        <v>5.062572920160188e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.105303804055527e-09</v>
+        <v>2.105303804055529e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>3.557666717537047e-09</v>
+        <v>3.557666717537014e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.075591757663107e-09</v>
+        <v>8.075591757662873e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.126263282970891e-09</v>
+        <v>2.126263282970851e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>3.737844684249549e-09</v>
+        <v>3.737844684249463e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.848627164264077e-09</v>
+        <v>6.848627164263994e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>4.614534042532538e-09</v>
+        <v>4.614534042532523e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.940528234521684e-09</v>
+        <v>8.940528234521568e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.268955034027379e-08</v>
+        <v>1.268955034027376e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.431650123397e-09</v>
+        <v>2.431650123396911e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.18370741418481e-09</v>
+        <v>3.183707414184704e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.504458020709808e-09</v>
+        <v>6.504458020709766e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.366819351234566e-09</v>
+        <v>3.366819351234493e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.482157672459972e-09</v>
+        <v>2.48215767245986e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>6.679971901420797e-09</v>
+        <v>6.679971901420758e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>3.333402492019883e-09</v>
+        <v>3.333402492019793e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.086004853019683e-08</v>
+        <v>1.086004853019671e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.771548994698119e-09</v>
+        <v>5.771548994698023e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.46740123358889e-09</v>
+        <v>4.4674012335889e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>8.972923399076877e-09</v>
+        <v>8.972923399076776e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.550600082264059e-08</v>
+        <v>1.550600082264042e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.471425658596293e-09</v>
+        <v>4.471425658596219e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.08937434413087e-09</v>
+        <v>4.089374344130818e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.067409082983543e-08</v>
+        <v>2.067409082983539e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.397754162611066e-09</v>
+        <v>3.397754162610886e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.148318616172416e-09</v>
+        <v>5.148318616172408e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.118167160048956e-09</v>
+        <v>4.118167160048943e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.637654435285658e-09</v>
+        <v>3.637654435285651e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.456947440376489e-09</v>
+        <v>5.456947440376535e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.071253403358129e-09</v>
+        <v>5.071253403358137e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.085296600719754e-09</v>
+        <v>5.085296600719744e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.781215043068606e-09</v>
+        <v>3.781215043068467e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.144533511456194e-09</v>
+        <v>4.144533511456174e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.055475375835675e-09</v>
+        <v>4.055475375835693e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.062576878084459e-09</v>
+        <v>3.06257687808451e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.270971014470343e-09</v>
+        <v>4.270971014470387e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.558311263780028e-09</v>
+        <v>4.558311263779932e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.103628064781645e-09</v>
+        <v>5.103628064781619e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.218892890392767e-09</v>
+        <v>3.218892890392716e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.799291574532039e-09</v>
+        <v>6.799291574532053e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.366072905338355e-09</v>
+        <v>3.36607290533839e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.103292877313476e-09</v>
+        <v>5.103292877313465e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.926020275172399e-09</v>
+        <v>6.926020275172387e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.849797231748164e-09</v>
+        <v>5.849797231748256e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.531062564046549e-09</v>
+        <v>4.531062564046602e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>5.682654433874694e-09</v>
+        <v>5.682654433874548e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.555844994530986e-09</v>
+        <v>4.555844994531052e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>5.117735859123041e-09</v>
+        <v>5.117735859123058e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>6.780864419490944e-09</v>
+        <v>6.780864419490776e-09</v>
       </c>
       <c r="H4" t="n">
         <v>4.612404051007723e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>5.199806547629538e-09</v>
+        <v>5.199806547629463e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.203070339398701e-09</v>
+        <v>6.203070339398714e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>5.519349524117477e-09</v>
+        <v>5.519349524117497e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.096123608709031e-09</v>
+        <v>7.096123608708907e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>8.451161297917158e-09</v>
+        <v>8.451161297917183e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.723713968309705e-09</v>
+        <v>4.723713968309563e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.997830019699288e-09</v>
+        <v>4.997830019699172e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.208204621555282e-09</v>
+        <v>6.208204621555148e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.064572170544999e-09</v>
+        <v>5.064572170544873e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.742123376853577e-09</v>
+        <v>4.742123376853511e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.27217737008641e-09</v>
+        <v>6.272177370086284e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>5.052392117761811e-09</v>
+        <v>5.052392117761669e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.795766216337307e-09</v>
+        <v>7.795766216337188e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>5.155529686033005e-09</v>
+        <v>5.155529686032857e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.465721342978198e-09</v>
+        <v>5.465721342978419e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>7.107931265786168e-09</v>
+        <v>7.107931265786044e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.489161271406849e-09</v>
+        <v>9.489161271406699e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.46718819863621e-09</v>
+        <v>5.467188198636039e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.327934980786595e-09</v>
+        <v>5.327934980786715e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.13990204432665e-08</v>
+        <v>1.139902044326648e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.075847546036837e-09</v>
+        <v>5.075847546036872e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.742522118958083e-09</v>
+        <v>5.742522118958105e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.289510051555725e-09</v>
+        <v>5.289510051555771e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.146890442979206e-09</v>
+        <v>5.146890442979255e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.826399315514052e-09</v>
+        <v>5.826399315514106e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.555238474524906e-09</v>
+        <v>5.555238474524923e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.679500103505357e-09</v>
+        <v>5.679500103505397e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.21561453413861e-09</v>
+        <v>5.215614534138497e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.348039849565042e-09</v>
+        <v>5.348039849564963e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.315579204904788e-09</v>
+        <v>5.31557920490473e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.95367936167728e-09</v>
+        <v>4.953679361677298e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.394124834709569e-09</v>
+        <v>5.39412483470957e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.713318779669954e-09</v>
+        <v>4.71331877966993e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.697618551995311e-09</v>
+        <v>5.697618551995382e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.010654712608359e-09</v>
+        <v>5.010654712608248e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.315667989813101e-09</v>
+        <v>6.315667989813119e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.064300099781041e-09</v>
+        <v>5.064300099780828e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.697496380099139e-09</v>
+        <v>5.697496380099197e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.388010164086942e-09</v>
+        <v>6.388010164086901e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6842,82 +6842,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.582712494076193e-09</v>
+        <v>2.582712494076145e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.263977826374575e-09</v>
+        <v>1.263977826374574e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.415569696202721e-09</v>
+        <v>2.41556969620258e-09</v>
       </c>
       <c r="E6" t="n">
         <v>1.288760256859015e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.850651121451064e-09</v>
+        <v>1.850651121451048e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.396901334259811e-09</v>
+        <v>3.396901334259649e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.345319313335742e-09</v>
+        <v>1.345319313335699e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.93272180995756e-09</v>
+        <v>1.932721809957431e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.933448837975018e-09</v>
+        <v>2.933448837975062e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.252264786445503e-09</v>
+        <v>2.252264786445506e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.829038871037053e-09</v>
+        <v>3.829038871036914e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.184076560245176e-09</v>
+        <v>5.184076560245157e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.456629230637734e-09</v>
+        <v>1.456629230637617e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.613866934468148e-09</v>
+        <v>1.613866934468025e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.824241536324148e-09</v>
+        <v>2.824241536323982e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.797487432873023e-09</v>
+        <v>1.797487432872881e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.475038639181595e-09</v>
+        <v>1.475038639181488e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.005092632414431e-09</v>
+        <v>3.005092632414317e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.785307380089845e-09</v>
+        <v>1.785307380089721e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.411803131106166e-09</v>
+        <v>4.411803131106037e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.51273009436006e-09</v>
+        <v>2.512730094359979e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.081758257747058e-09</v>
+        <v>2.081758257747252e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>3.723968180555026e-09</v>
+        <v>3.723968180554869e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.22207653373487e-09</v>
+        <v>6.222076533734694e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.200103460964239e-09</v>
+        <v>2.200103460964118e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.060850243114626e-09</v>
+        <v>2.060850243114655e-09</v>
       </c>
       <c r="AB6" t="n">
         <v>8.131935705594531e-09</v>
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.808762808364863e-09</v>
+        <v>1.808762808364899e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.475437381286099e-09</v>
+        <v>2.475437381286098e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.022425313883751e-09</v>
+        <v>2.022425313883747e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.87980570530723e-09</v>
+        <v>1.879805705307227e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.442436230282918e-09</v>
+        <v>2.442436230282953e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.285616973101235e-09</v>
+        <v>2.285616973101274e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.412415365833392e-09</v>
+        <v>2.412415365833386e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.948529796466636e-09</v>
+        <v>1.94852979646649e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.964076764333899e-09</v>
+        <v>1.964076764333793e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.931616119673648e-09</v>
+        <v>1.93161611967359e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.686594624005302e-09</v>
+        <v>1.68659462400524e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.01016174947843e-09</v>
+        <v>2.01016174947838e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.070519187997131e-09</v>
+        <v>2.070519187997126e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.313655466764173e-09</v>
+        <v>2.313655466764227e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.626691627377224e-09</v>
+        <v>1.626691627377101e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.048583252141132e-09</v>
+        <v>3.048583252141108e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.797215362109065e-09</v>
+        <v>1.797215362108865e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.430411642427163e-09</v>
+        <v>2.430411642427209e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.120925426414969e-09</v>
+        <v>3.120925426414964e-09</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="C8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="D8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="F8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="G8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="I8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="J8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="K8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="L8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155584e-09</v>
       </c>
       <c r="M8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="N8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="O8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="P8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="R8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="S8" t="n">
-        <v>2.027877732239054e-09</v>
+        <v>2.027877732239053e-09</v>
       </c>
       <c r="T8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="U8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="V8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="W8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="X8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.002775194155588e-09</v>
+        <v>2.002775194155583e-09</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.039523878899565e-09</v>
+        <v>6.039523878899572e-09</v>
       </c>
       <c r="C9" t="n">
-        <v>2.018441288226556e-09</v>
+        <v>2.018441288226547e-09</v>
       </c>
       <c r="D9" t="n">
-        <v>5.546699045848113e-09</v>
+        <v>5.546699045848086e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>2.451240133661649e-09</v>
+        <v>2.451240133661648e-09</v>
       </c>
       <c r="F9" t="n">
-        <v>3.95710211728381e-09</v>
+        <v>3.957102117283746e-09</v>
       </c>
       <c r="G9" t="n">
-        <v>8.784799398975432e-09</v>
+        <v>8.784799398975296e-09</v>
       </c>
       <c r="H9" t="n">
-        <v>2.391038299646179e-09</v>
+        <v>2.391038299646169e-09</v>
       </c>
       <c r="I9" t="n">
-        <v>4.123009649980999e-09</v>
+        <v>4.123009649980985e-09</v>
       </c>
       <c r="J9" t="n">
-        <v>7.500609800466937e-09</v>
+        <v>7.500609800466896e-09</v>
       </c>
       <c r="K9" t="n">
-        <v>5.065190324494139e-09</v>
+        <v>5.065190324494115e-09</v>
       </c>
       <c r="L9" t="n">
-        <v>9.714349216682501e-09</v>
+        <v>9.714349216682495e-09</v>
       </c>
       <c r="M9" t="n">
-        <v>1.37627751349955e-08</v>
+        <v>1.376277513499546e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.719238450111832e-09</v>
+        <v>2.719238450111827e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>3.527476669057183e-09</v>
+        <v>3.527476669057166e-09</v>
       </c>
       <c r="P9" t="n">
-        <v>7.096297274423405e-09</v>
+        <v>7.09629727442346e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.724267615281086e-09</v>
+        <v>3.724267615281083e-09</v>
       </c>
       <c r="R9" t="n">
-        <v>2.773519064099607e-09</v>
+        <v>2.773519064099601e-09</v>
       </c>
       <c r="S9" t="n">
-        <v>7.284922566783034e-09</v>
+        <v>7.284922566783023e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>3.688354416771798e-09</v>
+        <v>3.688354416771797e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.177726341751519e-08</v>
+        <v>1.177726341751515e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>6.39351161690285e-09</v>
+        <v>6.393511616902819e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>4.907066254817921e-09</v>
+        <v>4.90706625481792e-09</v>
       </c>
       <c r="X9" t="n">
-        <v>9.74916439688653e-09</v>
+        <v>9.749164396886507e-09</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.677028223688764e-08</v>
+        <v>1.677028223688749e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.911391316405794e-09</v>
+        <v>4.911391316405795e-09</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.500799626475098e-09</v>
+        <v>4.500799626475088e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.228022042631836e-08</v>
+        <v>2.228022042631834e-08</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.75751334955774e-09</v>
+        <v>3.757513349557733e-09</v>
       </c>
       <c r="C10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="D10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="E10" t="n">
-        <v>4.614470400499798e-09</v>
+        <v>4.61447040049979e-09</v>
       </c>
       <c r="F10" t="n">
-        <v>4.04306515669921e-09</v>
+        <v>4.043065156699205e-09</v>
       </c>
       <c r="G10" t="n">
-        <v>5.970534521843592e-09</v>
+        <v>5.970534521843583e-09</v>
       </c>
       <c r="H10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="I10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="J10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="K10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="L10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="M10" t="n">
-        <v>5.590460905547064e-09</v>
+        <v>5.590460905547057e-09</v>
       </c>
       <c r="N10" t="n">
-        <v>4.169619904274538e-09</v>
+        <v>4.169619904274532e-09</v>
       </c>
       <c r="O10" t="n">
-        <v>4.560079348517067e-09</v>
+        <v>4.560079348517055e-09</v>
       </c>
       <c r="P10" t="n">
-        <v>4.464368303895548e-09</v>
+        <v>4.464368303895536e-09</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.397297319748446e-09</v>
+        <v>3.397297319748441e-09</v>
       </c>
       <c r="R10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="S10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="T10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="U10" t="n">
-        <v>4.695962111035065e-09</v>
+        <v>4.695962111035054e-09</v>
       </c>
       <c r="V10" t="n">
-        <v>5.089641400090872e-09</v>
+        <v>5.08964140009086e-09</v>
       </c>
       <c r="W10" t="n">
-        <v>5.590821132521201e-09</v>
+        <v>5.590821132521189e-09</v>
       </c>
       <c r="X10" t="n">
-        <v>3.565290605537033e-09</v>
+        <v>3.565290605537021e-09</v>
       </c>
       <c r="Y10" t="n">
-        <v>7.413155776223183e-09</v>
+        <v>7.413155776223165e-09</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.723465407644674e-09</v>
+        <v>3.723465407644668e-09</v>
       </c>
       <c r="AA10" t="n">
-        <v>5.59046090554699e-09</v>
+        <v>5.590460905546978e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.505127896604433e-09</v>
+        <v>7.505127896604425e-09</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="C11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="D11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="E11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="F11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="G11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="H11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="I11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="J11" t="n">
-        <v>4.243187540332585e-09</v>
+        <v>4.243187540332569e-09</v>
       </c>
       <c r="K11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="L11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.33796142428601e-09</v>
       </c>
       <c r="M11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="N11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="O11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="P11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="R11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="S11" t="n">
-        <v>4.350299960203424e-09</v>
+        <v>4.350299960203463e-09</v>
       </c>
       <c r="T11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="U11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="V11" t="n">
-        <v>3.705654850858866e-09</v>
+        <v>3.705654850858983e-09</v>
       </c>
       <c r="W11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="X11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.337961424285982e-09</v>
+        <v>4.337961424286011e-09</v>
       </c>
     </row>
     <row r="12">
@@ -7370,82 +7370,82 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6.322126072131477e-09</v>
+        <v>6.322126072131473e-09</v>
       </c>
       <c r="C12" t="n">
-        <v>4.345661707967977e-09</v>
+        <v>4.345661707968009e-09</v>
       </c>
       <c r="D12" t="n">
-        <v>6.079890132347409e-09</v>
+        <v>6.079890132347472e-09</v>
       </c>
       <c r="E12" t="n">
-        <v>4.558393348158035e-09</v>
+        <v>4.558393348158073e-09</v>
       </c>
       <c r="F12" t="n">
-        <v>5.298562812690123e-09</v>
+        <v>5.298562812690136e-09</v>
       </c>
       <c r="G12" t="n">
-        <v>7.671498812653137e-09</v>
+        <v>7.671498812653081e-09</v>
       </c>
       <c r="H12" t="n">
-        <v>4.528802615586455e-09</v>
+        <v>4.528802615586494e-09</v>
       </c>
       <c r="I12" t="n">
-        <v>5.380110584646583e-09</v>
+        <v>5.380110584646556e-09</v>
       </c>
       <c r="J12" t="n">
-        <v>6.945513079391061e-09</v>
+        <v>6.945513079391073e-09</v>
       </c>
       <c r="K12" t="n">
-        <v>5.843216349272783e-09</v>
+        <v>5.843216349272851e-09</v>
       </c>
       <c r="L12" t="n">
-        <v>8.128396189910229e-09</v>
+        <v>8.128396189910267e-09</v>
       </c>
       <c r="M12" t="n">
         <v>1.011830049504968e-08</v>
       </c>
       <c r="N12" t="n">
-        <v>4.690121336871376e-09</v>
+        <v>4.69012133687141e-09</v>
       </c>
       <c r="O12" t="n">
-        <v>5.087390977939133e-09</v>
+        <v>5.087390977939137e-09</v>
       </c>
       <c r="P12" t="n">
-        <v>6.841557073646744e-09</v>
+        <v>6.841557073646795e-09</v>
       </c>
       <c r="Q12" t="n">
-        <v>5.184118733122212e-09</v>
+        <v>5.184118733122236e-09</v>
       </c>
       <c r="R12" t="n">
-        <v>4.716801639201049e-09</v>
+        <v>4.716801639201039e-09</v>
       </c>
       <c r="S12" t="n">
-        <v>6.934271202273076e-09</v>
+        <v>6.934271202273112e-09</v>
       </c>
       <c r="T12" t="n">
-        <v>5.166466482650807e-09</v>
+        <v>5.166466482650839e-09</v>
       </c>
       <c r="U12" t="n">
-        <v>9.14237098707802e-09</v>
+        <v>9.142370987078038e-09</v>
       </c>
       <c r="V12" t="n">
-        <v>5.863813475137367e-09</v>
+        <v>5.863813475136925e-09</v>
       </c>
       <c r="W12" t="n">
-        <v>5.765494347353093e-09</v>
+        <v>5.765494347353072e-09</v>
       </c>
       <c r="X12" t="n">
-        <v>8.145508736457973e-09</v>
+        <v>8.14550873645794e-09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.159656672754296e-08</v>
+        <v>1.159656672754291e-08</v>
       </c>
       <c r="Z12" t="n">
-        <v>5.767620225125674e-09</v>
+        <v>5.7676202251257e-09</v>
       </c>
       <c r="AA12" t="n">
-        <v>5.565803966675274e-09</v>
+        <v>5.565803966675365e-09</v>
       </c>
       <c r="AB12" t="n">
         <v>1.430484148554304e-08</v>
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>5.200459857079893e-09</v>
+        <v>5.200459857079909e-09</v>
       </c>
       <c r="C13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="D13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="E13" t="n">
-        <v>5.621676043172227e-09</v>
+        <v>5.621676043172257e-09</v>
       </c>
       <c r="F13" t="n">
-        <v>5.340815832917518e-09</v>
+        <v>5.340815832917513e-09</v>
       </c>
       <c r="G13" t="n">
-        <v>6.288216048486609e-09</v>
+        <v>6.288216048486652e-09</v>
       </c>
       <c r="H13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="I13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="J13" t="n">
-        <v>6.006626315460278e-09</v>
+        <v>6.006626315460259e-09</v>
       </c>
       <c r="K13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="L13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="M13" t="n">
-        <v>6.101400199413711e-09</v>
+        <v>6.101400199413775e-09</v>
       </c>
       <c r="N13" t="n">
-        <v>5.403020710101223e-09</v>
+        <v>5.403020710101173e-09</v>
       </c>
       <c r="O13" t="n">
-        <v>5.594941457759194e-09</v>
+        <v>5.594941457759218e-09</v>
       </c>
       <c r="P13" t="n">
-        <v>5.547897045045549e-09</v>
+        <v>5.54789704504558e-09</v>
       </c>
       <c r="Q13" t="n">
-        <v>5.023404516816568e-09</v>
+        <v>5.023404516816577e-09</v>
       </c>
       <c r="R13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="S13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="T13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="U13" t="n">
-        <v>5.661731291532782e-09</v>
+        <v>5.661731291532801e-09</v>
       </c>
       <c r="V13" t="n">
-        <v>5.222928101382005e-09</v>
+        <v>5.222928101381948e-09</v>
       </c>
       <c r="W13" t="n">
-        <v>6.101577260133383e-09</v>
+        <v>6.10157726013338e-09</v>
       </c>
       <c r="X13" t="n">
-        <v>5.10597748946578e-09</v>
+        <v>5.105977489465779e-09</v>
       </c>
       <c r="Y13" t="n">
-        <v>6.99730108615276e-09</v>
+        <v>6.997301086152766e-09</v>
       </c>
       <c r="Z13" t="n">
-        <v>5.183724427665832e-09</v>
+        <v>5.183724427665828e-09</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.101400199413673e-09</v>
+        <v>6.101400199413732e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.042507722507798e-09</v>
+        <v>7.042507722507827e-09</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="C14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="D14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="E14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="F14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="G14" t="n">
-        <v>1.42818429491138e-09</v>
+        <v>1.428184294911375e-09</v>
       </c>
       <c r="H14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="I14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="J14" t="n">
-        <v>1.431729680494041e-09</v>
+        <v>1.431729680494037e-09</v>
       </c>
       <c r="K14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="L14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="M14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="N14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="O14" t="n">
-        <v>1.42818429491138e-09</v>
+        <v>1.428184294911375e-09</v>
       </c>
       <c r="P14" t="n">
-        <v>1.42818429491138e-09</v>
+        <v>1.428184294911375e-09</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="R14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="S14" t="n">
-        <v>1.541023319185518e-09</v>
+        <v>1.541023319185515e-09</v>
       </c>
       <c r="T14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="U14" t="n">
-        <v>1.428184294911379e-09</v>
+        <v>1.428184294911375e-09</v>
       </c>
       <c r="V14" t="n">
-        <v>1.433183900194478e-09</v>
+        <v>1.433183900194476e-09</v>
       </c>
       <c r="W14" t="n">
-        <v>1.42818429491138e-09</v>
+        <v>1.428184294911375e-09</v>
       </c>
       <c r="X14" t="n">
-        <v>1.42818429491138e-09</v>
+        <v>1.428184294911375e-09</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.528684783268075e-09</v>
+        <v>1.52868478326807e-09</v>
       </c>
     </row>
     <row r="15">
@@ -7634,79 +7634,79 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.512849431113562e-09</v>
+        <v>3.512849431113565e-09</v>
       </c>
       <c r="C15" t="n">
-        <v>1.536385066950067e-09</v>
+        <v>1.536385066950065e-09</v>
       </c>
       <c r="D15" t="n">
-        <v>3.270613491329501e-09</v>
+        <v>3.270613491329487e-09</v>
       </c>
       <c r="E15" t="n">
-        <v>1.749116707140129e-09</v>
+        <v>1.749116707140125e-09</v>
       </c>
       <c r="F15" t="n">
-        <v>2.489286171672217e-09</v>
+        <v>2.489286171672198e-09</v>
       </c>
       <c r="G15" t="n">
-        <v>4.761721683278518e-09</v>
+        <v>4.761721683278461e-09</v>
       </c>
       <c r="H15" t="n">
-        <v>1.719525974568539e-09</v>
+        <v>1.719525974568538e-09</v>
       </c>
       <c r="I15" t="n">
-        <v>2.570833943628675e-09</v>
+        <v>2.570833943628676e-09</v>
       </c>
       <c r="J15" t="n">
-        <v>4.134055219552548e-09</v>
+        <v>4.134055219552534e-09</v>
       </c>
       <c r="K15" t="n">
-        <v>3.033939708254882e-09</v>
+        <v>3.033939708254874e-09</v>
       </c>
       <c r="L15" t="n">
-        <v>5.319119548892323e-09</v>
+        <v>5.31911954889232e-09</v>
       </c>
       <c r="M15" t="n">
-        <v>7.309023854031785e-09</v>
+        <v>7.309023854031761e-09</v>
       </c>
       <c r="N15" t="n">
-        <v>1.880844695853472e-09</v>
+        <v>1.880844695853463e-09</v>
       </c>
       <c r="O15" t="n">
-        <v>2.177613848564529e-09</v>
+        <v>2.177613848564511e-09</v>
       </c>
       <c r="P15" t="n">
-        <v>3.931779944272148e-09</v>
+        <v>3.931779944272117e-09</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.374842092104306e-09</v>
+        <v>2.374842092104304e-09</v>
       </c>
       <c r="R15" t="n">
-        <v>1.907524998183145e-09</v>
+        <v>1.907524998183144e-09</v>
       </c>
       <c r="S15" t="n">
-        <v>4.124994561255164e-09</v>
+        <v>4.124994561255167e-09</v>
       </c>
       <c r="T15" t="n">
-        <v>2.357189841632904e-09</v>
+        <v>2.357189841632902e-09</v>
       </c>
       <c r="U15" t="n">
-        <v>6.232593857703424e-09</v>
+        <v>6.232593857703412e-09</v>
       </c>
       <c r="V15" t="n">
-        <v>3.591342524472383e-09</v>
+        <v>3.591342524472373e-09</v>
       </c>
       <c r="W15" t="n">
-        <v>2.855717217978494e-09</v>
+        <v>2.855717217978485e-09</v>
       </c>
       <c r="X15" t="n">
-        <v>5.235731607083371e-09</v>
+        <v>5.235731607083351e-09</v>
       </c>
       <c r="Y15" t="n">
-        <v>8.787290086525045e-09</v>
+        <v>8.787290086524974e-09</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.95834358410777e-09</v>
+        <v>2.958343584107768e-09</v>
       </c>
       <c r="AA15" t="n">
         <v>2.756527325657362e-09</v>
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.391183216061985e-09</v>
+        <v>2.391183216061983e-09</v>
       </c>
       <c r="C16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="D16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="E16" t="n">
-        <v>2.81239940215433e-09</v>
+        <v>2.812399402154324e-09</v>
       </c>
       <c r="F16" t="n">
-        <v>2.531539191899614e-09</v>
+        <v>2.531539191899609e-09</v>
       </c>
       <c r="G16" t="n">
-        <v>3.378438919112007e-09</v>
+        <v>3.378438919112002e-09</v>
       </c>
       <c r="H16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="I16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="J16" t="n">
-        <v>3.195168455621731e-09</v>
+        <v>3.195168455621724e-09</v>
       </c>
       <c r="K16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="L16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="M16" t="n">
-        <v>3.292123558395802e-09</v>
+        <v>3.292123558395793e-09</v>
       </c>
       <c r="N16" t="n">
-        <v>2.593744069083316e-09</v>
+        <v>2.593744069083312e-09</v>
       </c>
       <c r="O16" t="n">
-        <v>2.685164328384596e-09</v>
+        <v>2.685164328384591e-09</v>
       </c>
       <c r="P16" t="n">
-        <v>2.638119915670947e-09</v>
+        <v>2.638119915670942e-09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.214127875798663e-09</v>
+        <v>2.214127875798659e-09</v>
       </c>
       <c r="R16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="S16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="T16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="U16" t="n">
-        <v>2.751954162158188e-09</v>
+        <v>2.751954162158181e-09</v>
       </c>
       <c r="V16" t="n">
-        <v>2.950457150717426e-09</v>
+        <v>2.950457150717418e-09</v>
       </c>
       <c r="W16" t="n">
-        <v>3.191800130758779e-09</v>
+        <v>3.191800130758772e-09</v>
       </c>
       <c r="X16" t="n">
-        <v>2.196200360091179e-09</v>
+        <v>2.196200360091176e-09</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.188024445134856e-09</v>
+        <v>4.188024445134849e-09</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.374447786647933e-09</v>
+        <v>2.374447786647927e-09</v>
       </c>
       <c r="AA16" t="n">
-        <v>3.292123558395763e-09</v>
+        <v>3.292123558395756e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.233231081489896e-09</v>
+        <v>4.233231081489886e-09</v>
       </c>
     </row>
   </sheetData>
@@ -9517,7 +9517,7 @@
         <v>2.307945724193067e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.608842774769533e-09</v>
+        <v>2.608842774769532e-09</v>
       </c>
       <c r="AB2" t="n">
         <v>1.855656097773328e-09</v>
@@ -9554,7 +9554,7 @@
         <v>4.942077609480297e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.911828248655586e-09</v>
+        <v>4.911828248655585e-09</v>
       </c>
       <c r="K3" t="n">
         <v>4.942077609480297e-09</v>
@@ -9624,7 +9624,7 @@
         <v>4.071176339135228e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.16181112486979e-09</v>
+        <v>4.161811124869791e-09</v>
       </c>
       <c r="E4" t="n">
         <v>3.877959025053003e-09</v>
@@ -9648,7 +9648,7 @@
         <v>4.213288523011081e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>4.178858616958399e-09</v>
+        <v>4.1788586169584e-09</v>
       </c>
       <c r="M4" t="n">
         <v>4.142584471818313e-09</v>
@@ -9660,13 +9660,13 @@
         <v>4.214144003950793e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.087308597652408e-09</v>
+        <v>4.087308597652409e-09</v>
       </c>
       <c r="Q4" t="n">
         <v>4.076110364996183e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.225828245381928e-09</v>
+        <v>4.225828245381927e-09</v>
       </c>
       <c r="S4" t="n">
         <v>4.195705666970141e-09</v>
@@ -9775,7 +9775,7 @@
         <v>4.557921741276781e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.836356129675154e-09</v>
+        <v>5.836356129675155e-09</v>
       </c>
       <c r="Z5" t="n">
         <v>4.610475192224293e-09</v>
@@ -9784,7 +9784,7 @@
         <v>5.230782946774437e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.854636616116163e-09</v>
+        <v>5.854636616116162e-09</v>
       </c>
     </row>
     <row r="6">
@@ -9945,7 +9945,7 @@
         <v>1.97624952017202e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.20922245550639e-09</v>
+        <v>2.209222455506389e-09</v>
       </c>
       <c r="X7" t="n">
         <v>1.536241564882049e-09</v>
@@ -10097,7 +10097,7 @@
         <v>2.475233631396071e-09</v>
       </c>
       <c r="O9" t="n">
-        <v>2.421314049540673e-09</v>
+        <v>2.421314049540672e-09</v>
       </c>
       <c r="P9" t="n">
         <v>2.04733659595397e-09</v>
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.623261644997333e-09</v>
+        <v>3.623261644997334e-09</v>
       </c>
       <c r="C10" t="n">
         <v>5.418900087616803e-09</v>
@@ -10337,7 +10337,7 @@
         <v>4.033722685238663e-09</v>
       </c>
       <c r="G12" t="n">
-        <v>4.31688980697407e-09</v>
+        <v>4.316889806974069e-09</v>
       </c>
       <c r="H12" t="n">
         <v>4.233046934228054e-09</v>
@@ -10352,7 +10352,7 @@
         <v>4.192520275829947e-09</v>
       </c>
       <c r="L12" t="n">
-        <v>4.142621861088203e-09</v>
+        <v>4.142621861088202e-09</v>
       </c>
       <c r="M12" t="n">
         <v>4.142741134534276e-09</v>
@@ -10361,7 +10361,7 @@
         <v>4.220262949137697e-09</v>
       </c>
       <c r="O12" t="n">
-        <v>4.193760103283397e-09</v>
+        <v>4.193760103283396e-09</v>
       </c>
       <c r="P12" t="n">
         <v>4.009940673230169e-09</v>
@@ -10397,7 +10397,7 @@
         <v>4.275685903819221e-09</v>
       </c>
       <c r="AA12" t="n">
-        <v>4.434632921214201e-09</v>
+        <v>4.4346329212142e-09</v>
       </c>
       <c r="AB12" t="n">
         <v>4.043260337961249e-09</v>
@@ -10425,7 +10425,7 @@
         <v>4.922046987227715e-09</v>
       </c>
       <c r="G13" t="n">
-        <v>5.850163147486879e-09</v>
+        <v>5.85016314748688e-09</v>
       </c>
       <c r="H13" t="n">
         <v>5.667149880582229e-09</v>
@@ -10473,10 +10473,10 @@
         <v>4.836662059140438e-09</v>
       </c>
       <c r="W13" t="n">
-        <v>5.667323337288004e-09</v>
+        <v>5.667323337288003e-09</v>
       </c>
       <c r="X13" t="n">
-        <v>4.691988709824773e-09</v>
+        <v>4.691988709824774e-09</v>
       </c>
       <c r="Y13" t="n">
         <v>6.544792177673767e-09</v>
@@ -10607,7 +10607,7 @@
         <v>1.734498955561716e-09</v>
       </c>
       <c r="I15" t="n">
-        <v>1.675260168429314e-09</v>
+        <v>1.675260168429313e-09</v>
       </c>
       <c r="J15" t="n">
         <v>1.643602769151638e-09</v>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide human toxicity non-carcinogenic results.xlsx
@@ -586,34 +586,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.515224786636162e-09</v>
+        <v>8.515224786636107e-09</v>
       </c>
       <c r="C2" t="n">
         <v>1.86179382645712e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>3.635650331734613e-09</v>
+        <v>3.635650331734564e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>3.035947582964403e-09</v>
+        <v>3.03594758296439e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>2.961440891007436e-09</v>
+        <v>2.961440891007435e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.633409553985487e-09</v>
+        <v>9.633409553985427e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.785810413348148e-09</v>
+        <v>2.785810413348074e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.637334605242486e-09</v>
+        <v>2.637334605242681e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.43321238530369e-09</v>
+        <v>7.43321238530366e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>3.337083339854275e-09</v>
+        <v>3.337083339854225e-09</v>
       </c>
       <c r="L2" t="n">
         <v>1.17690120199372e-08</v>
@@ -622,46 +622,46 @@
         <v>1.776063929260964e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.999020620131809e-09</v>
+        <v>2.999020620131711e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>4.983224630428153e-09</v>
+        <v>4.98322463042811e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>5.979175860379021e-09</v>
+        <v>5.979175860378955e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.301225675556624e-09</v>
+        <v>3.301225675556586e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.395059647628723e-09</v>
+        <v>2.395059647628676e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.487074184512535e-09</v>
+        <v>7.487074184512502e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>2.994408957014664e-09</v>
+        <v>2.994408957014628e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.518731752627373e-08</v>
+        <v>1.518731752627368e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>4.302492143193856e-09</v>
+        <v>4.302492143193852e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.65131866611284e-09</v>
+        <v>4.65131866611281e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>6.046124829551643e-09</v>
+        <v>6.046124829551532e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.772845261750716e-09</v>
+        <v>6.77284526175059e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.205975779755727e-09</v>
+        <v>5.20597577975573e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.697953469018643e-09</v>
+        <v>4.697953469018605e-09</v>
       </c>
       <c r="AB2" t="n">
         <v>2.496300735226856e-08</v>
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.393177319626075e-09</v>
+        <v>3.393177319626314e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.132215576281364e-09</v>
+        <v>5.132215576281366e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="E3" t="n">
         <v>4.107913099761049e-09</v>
@@ -689,70 +689,70 @@
         <v>3.626637891689274e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.441185126751229e-09</v>
+        <v>5.441185126751187e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.055586967689519e-09</v>
+        <v>5.055586967689456e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.082835774301542e-09</v>
+        <v>5.082835774301544e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.774555253104649e-09</v>
+        <v>3.774555253104704e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.135900187438863e-09</v>
+        <v>4.135900187438569e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.04732581270174e-09</v>
+        <v>4.047325812701541e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.059820707162061e-09</v>
+        <v>3.059820707161966e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.261465004013039e-09</v>
+        <v>4.2614650040134e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.540891750429724e-09</v>
+        <v>4.540891750429726e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.089784970472208e-09</v>
+        <v>5.08978497047207e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.215287615999526e-09</v>
+        <v>3.215287615999636e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.775919701297381e-09</v>
+        <v>6.775919701297419e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.361668153907849e-09</v>
+        <v>3.361668153907828e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.089451603725773e-09</v>
+        <v>5.089451603725604e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.914558693680186e-09</v>
+        <v>6.914558693680191e-09</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.025493593249379e-09</v>
+        <v>7.025493593249345e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.627573143513996e-09</v>
+        <v>4.627573143513945e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>5.246946003293913e-09</v>
+        <v>5.246946003293845e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.978586534764955e-09</v>
+        <v>4.978586534764915e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.981631366112589e-09</v>
+        <v>4.981631366112556e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.433058810559748e-09</v>
+        <v>7.433058810559708e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.937189332366202e-09</v>
+        <v>4.937189332366144e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.883071643802655e-09</v>
+        <v>4.88307164380255e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.470191112598193e-09</v>
+        <v>6.470191112598279e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>5.138121840704154e-09</v>
+        <v>5.138121840704078e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>8.211460831888883e-09</v>
+        <v>8.211460831888815e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.039113417825226e-08</v>
+        <v>1.039113417825222e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>5.0149019490982e-09</v>
+        <v>5.014901949098464e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.738121011151368e-09</v>
+        <v>5.738121011151315e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.101133539418659e-09</v>
+        <v>6.10113353941861e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.125052143129617e-09</v>
+        <v>5.125052143129546e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.794765266688623e-09</v>
+        <v>4.794765266688553e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.65074477192924e-09</v>
+        <v>6.650744771929145e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>5.013221052044879e-09</v>
+        <v>5.013221052044815e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>9.457393049178709e-09</v>
+        <v>9.457393049178628e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>4.506017397327494e-09</v>
+        <v>4.506017397327496e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.617145184595047e-09</v>
+        <v>5.617145184594959e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>6.125535652527598e-09</v>
+        <v>6.12553565252742e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.390416716482001e-09</v>
+        <v>6.390416716481705e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.819311189405217e-09</v>
+        <v>5.819311189405158e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.634143022640708e-09</v>
+        <v>5.63414302264064e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.305433071946697e-08</v>
+        <v>1.305433071946694e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.158567437642215e-09</v>
+        <v>5.158567437642159e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.819603468093848e-09</v>
+        <v>5.8196034680938e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.369305377982712e-09</v>
+        <v>5.369305377982668e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.224087861723568e-09</v>
+        <v>5.224087861723531e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.905042234417481e-09</v>
+        <v>5.905042234417347e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.603574567365071e-09</v>
+        <v>5.603574567365143e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.770223666114019e-09</v>
+        <v>5.770223666113989e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.297575216029352e-09</v>
+        <v>5.297575216029155e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.429281201467728e-09</v>
+        <v>5.42928120146759e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.396996881968869e-09</v>
+        <v>5.396996881968725e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.037062866870053e-09</v>
+        <v>5.037062866870238e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.475048102652497e-09</v>
+        <v>5.475048102652512e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.592911254735446e-09</v>
+        <v>4.592911254735443e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.77696100380274e-09</v>
+        <v>5.776961003802793e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.093728729556698e-09</v>
+        <v>5.093728729556441e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.391537313594871e-09</v>
+        <v>6.391537313594746e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.147082716737226e-09</v>
+        <v>5.147082716737244e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.776839495538256e-09</v>
+        <v>5.776839495538361e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.475883118995831e-09</v>
+        <v>6.47588311899579e-09</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.680538387173561e-09</v>
+        <v>3.680538387173552e-09</v>
       </c>
       <c r="C6" t="n">
         <v>1.282617937438173e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.901990797218094e-09</v>
+        <v>1.901990797218035e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.633631328689136e-09</v>
+        <v>1.633631328689133e-09</v>
       </c>
       <c r="F6" t="n">
         <v>1.636676160036763e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.971065219250831e-09</v>
+        <v>3.97106521925081e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.592234126290383e-09</v>
+        <v>1.592234126290349e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.538116437726832e-09</v>
+        <v>1.538116437726771e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.151721584953268e-09</v>
+        <v>3.151721584953208e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.793166634628334e-09</v>
+        <v>1.793166634628329e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.866505625813066e-09</v>
+        <v>4.866505625813057e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>7.046178972176446e-09</v>
+        <v>7.046178972176447e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.669946743022374e-09</v>
+        <v>1.66994674302264e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>2.276127419842453e-09</v>
+        <v>2.276127419842449e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.639139948109748e-09</v>
+        <v>2.639139948109717e-09</v>
       </c>
       <c r="Q6" t="n">
         <v>1.780096937053796e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.449810060612802e-09</v>
+        <v>1.449810060612759e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.30578956585342e-09</v>
+        <v>3.305789565853393e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.66826584596906e-09</v>
+        <v>1.66826584596902e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.995399457869794e-09</v>
+        <v>5.99539945786978e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.979876660401452e-09</v>
+        <v>1.979876660401448e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.155151593286135e-09</v>
+        <v>2.155151593286137e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.663542061218687e-09</v>
+        <v>2.663542061218589e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.045461510406188e-09</v>
+        <v>3.045461510405899e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.474355983329397e-09</v>
+        <v>2.474355983329364e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.289187816564888e-09</v>
+        <v>2.289187816564878e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.709375513391154e-09</v>
+        <v>9.709375513391157e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.81361223156639e-09</v>
+        <v>1.813612231566372e-09</v>
       </c>
       <c r="C7" t="n">
         <v>2.474648262018028e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.02435017190689e-09</v>
+        <v>2.024350171906889e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.879132655647746e-09</v>
+        <v>1.879132655647744e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.443048643108569e-09</v>
+        <v>2.443048643108493e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.285105039720146e-09</v>
+        <v>2.28510503972021e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.425268460038197e-09</v>
+        <v>2.425268460038195e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.952620009953532e-09</v>
+        <v>1.952620009953376e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.967287610158816e-09</v>
+        <v>1.967287610158708e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.935003290659956e-09</v>
+        <v>1.935003290659824e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.692107660794234e-09</v>
+        <v>1.692107660794441e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.013054511343586e-09</v>
+        <v>2.013054511343654e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.066770517809398e-09</v>
+        <v>2.066770517809397e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.314967412493828e-09</v>
+        <v>2.314967412493942e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.631735138247784e-09</v>
+        <v>1.631735138247557e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.046582107519049e-09</v>
+        <v>3.046582107518972e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.802127510661403e-09</v>
+        <v>1.802127510661448e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.431884289462434e-09</v>
+        <v>2.431884289462563e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.130927912920008e-09</v>
+        <v>3.130927912920006e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1270,82 +1270,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.677258568163831e-09</v>
+        <v>1.677258568162969e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.663237072724097e-09</v>
+        <v>1.663237072724101e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.126883930610836e-09</v>
+        <v>2.126883930609948e-09</v>
       </c>
       <c r="E2" t="n">
         <v>1.17168216666732e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.733079222765016e-09</v>
+        <v>1.733079222765014e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>2.586133936723352e-09</v>
+        <v>2.586133936722548e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.10286163295766e-09</v>
+        <v>2.102861632956793e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.089055025974278e-09</v>
+        <v>2.089055025973401e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>2.30260265840873e-09</v>
+        <v>2.302602658408511e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>2.210914928258061e-09</v>
+        <v>2.210914928257196e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.170481758448991e-09</v>
+        <v>2.170481758447972e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>2.372126786642465e-09</v>
+        <v>2.372126786642463e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>1.968196800934221e-09</v>
+        <v>1.968196800934563e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.700365620694297e-09</v>
+        <v>1.700365620693339e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.892005490987233e-09</v>
+        <v>1.892005490987183e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.873352378964869e-09</v>
+        <v>1.87335237896399e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.143023773109174e-09</v>
+        <v>2.143023773108315e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>2.17416192985606e-09</v>
+        <v>2.174161929855293e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.932270506666625e-09</v>
+        <v>1.932270506666091e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>2.743776260771714e-09</v>
+        <v>2.743776260770836e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>2.256319109518751e-09</v>
+        <v>2.25631910951875e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>3.252228582612008e-09</v>
+        <v>3.252228582611675e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>6.000192586841033e-09</v>
+        <v>6.000192586840131e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.684656944406825e-09</v>
+        <v>5.684656944405914e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.875523737516928e-09</v>
+        <v>1.875523737516536e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.934497111361817e-09</v>
+        <v>2.934497111361227e-09</v>
       </c>
       <c r="AB2" t="n">
         <v>2.331572400842566e-09</v>
@@ -1358,82 +1358,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.282320627603927e-09</v>
+        <v>3.282320627603247e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.014944837989344e-09</v>
+        <v>5.014944837989343e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.001088350100347e-09</v>
+        <v>4.001088350100348e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.52452349733495e-09</v>
+        <v>3.524523497334942e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.307262853043486e-09</v>
+        <v>5.307262853043337e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.929771001801712e-09</v>
+        <v>4.929771001801401e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.924943409724555e-09</v>
+        <v>4.924943409724553e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65940331189228e-09</v>
+        <v>3.659403311891867e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.016678617651788e-09</v>
+        <v>4.016678617651151e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.92910180721437e-09</v>
+        <v>3.929101807213597e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.952718426692074e-09</v>
+        <v>2.952718426692155e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.140980968989107e-09</v>
+        <v>4.140980968988975e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.430062232591464e-09</v>
+        <v>4.43006223259146e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.959820322801057e-09</v>
+        <v>4.959820322801005e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.106434397538459e-09</v>
+        <v>3.106434397537793e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.627224566665869e-09</v>
+        <v>6.627224566665687e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.251166332229222e-09</v>
+        <v>3.251166332228731e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.959490710573909e-09</v>
+        <v>4.959490710573897e-09</v>
       </c>
       <c r="AB3" t="n">
         <v>6.701682404722789e-09</v>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.044282793391774e-09</v>
+        <v>4.04428279339082e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.074413872099785e-09</v>
+        <v>4.074413872099817e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.208165958236133e-09</v>
+        <v>4.208165958235077e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.81846986939885e-09</v>
+        <v>3.818469869398882e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.052502803540542e-09</v>
+        <v>4.052502803540557e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>4.375557192678278e-09</v>
+        <v>4.37555719267719e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.199410112825581e-09</v>
+        <v>4.199410112824656e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.194377766705541e-09</v>
+        <v>4.194377766704589e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>4.152808045759918e-09</v>
+        <v>4.152808045759834e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.238794270136736e-09</v>
+        <v>4.238794270135804e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>4.224056854531229e-09</v>
+        <v>4.224056854530545e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.275598884107376e-09</v>
+        <v>4.275598884107384e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.1503263628673e-09</v>
+        <v>4.150326362866849e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.052705042702428e-09</v>
+        <v>4.05270504270148e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.122555525074572e-09</v>
+        <v>4.122555525074566e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.115756684778981e-09</v>
+        <v>4.115756684778014e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.214048741303176e-09</v>
+        <v>4.214048741302214e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>4.225398233794675e-09</v>
+        <v>4.225398233793816e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.137231650473893e-09</v>
+        <v>4.137231650473842e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>4.433015968664316e-09</v>
+        <v>4.433015968663349e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.539504174547246e-09</v>
+        <v>3.539504174547258e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>4.618340869426372e-09</v>
+        <v>4.618340869425735e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>5.619941480745489e-09</v>
+        <v>5.619941480744529e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>5.504932444284779e-09</v>
+        <v>5.504932444283857e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.116548119473349e-09</v>
+        <v>4.116548119473036e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.502531479146564e-09</v>
+        <v>4.502531479146269e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.276574546416251e-09</v>
+        <v>4.276574546416224e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.629309066466608e-09</v>
+        <v>4.629309066466553e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.296071994799363e-09</v>
+        <v>5.296071994799333e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.849755198695419e-09</v>
+        <v>4.849755198695376e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.705463205420518e-09</v>
+        <v>4.705463205420559e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.367376729567527e-09</v>
+        <v>5.367376729567337e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.110380057158326e-09</v>
+        <v>5.110380057158284e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.206070566534601e-09</v>
+        <v>5.206070566534554e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>4.766751276961564e-09</v>
+        <v>4.766751276961296e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>4.896973930572136e-09</v>
+        <v>4.896973930572102e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>4.865053211547153e-09</v>
+        <v>4.865053211546432e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.509172934619078e-09</v>
+        <v>4.509172934618884e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>4.942280678003046e-09</v>
+        <v>4.942280678002823e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.331808017526785e-09</v>
+        <v>4.331808017526792e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.240738007170582e-09</v>
+        <v>5.240738007170173e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.565200600968686e-09</v>
+        <v>4.565200600968053e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.848487274409848e-09</v>
+        <v>5.848487274409697e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.617953691635073e-09</v>
+        <v>4.617953691634725e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.240617867383934e-09</v>
+        <v>5.240617867383887e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.869428326407987e-09</v>
+        <v>5.869428326408046e-09</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.135803974331108e-09</v>
+        <v>1.135803974330105e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.165935053039195e-09</v>
+        <v>1.165935053039198e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.29968713917548e-09</v>
+        <v>1.299687139174555e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.099910503382555e-10</v>
+        <v>9.099910503382572e-10</v>
       </c>
       <c r="F6" t="n">
         <v>1.14402398447994e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.351073189125933e-09</v>
+        <v>1.351073189124854e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.290931293764948e-09</v>
+        <v>1.290931293763955e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.285898947644857e-09</v>
+        <v>1.285898947643858e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.232929364478507e-09</v>
+        <v>1.232929364478266e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.330315451076102e-09</v>
+        <v>1.330315451075092e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.315578035470603e-09</v>
+        <v>1.315578035470134e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.367120065046759e-09</v>
+        <v>1.367120065046752e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.241847543806703e-09</v>
+        <v>1.24184754380614e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.028221039150032e-09</v>
+        <v>1.028221039149133e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.098071521522146e-09</v>
+        <v>1.098071521522224e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.207277865718302e-09</v>
+        <v>1.207277865717304e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.305569922242524e-09</v>
+        <v>1.305569922241421e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.316919414734071e-09</v>
+        <v>1.316919414733088e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.228752831413247e-09</v>
+        <v>1.228752831413124e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.408531965111912e-09</v>
+        <v>1.408531965111002e-09</v>
       </c>
       <c r="V6" t="n">
         <v>1.191409260124954e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.593856865874011e-09</v>
+        <v>1.59385686587338e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.595457477193107e-09</v>
+        <v>2.595457477192168e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.596453625224122e-09</v>
+        <v>2.596453625223159e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.208069300412663e-09</v>
+        <v>1.208069300412331e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.594052660085905e-09</v>
+        <v>1.594052660085726e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.368095727355607e-09</v>
+        <v>1.368095727355606e-09</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.720830247405993e-09</v>
+        <v>1.720830247405779e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.38759317573871e-09</v>
+        <v>2.387593175738711e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.941276379634752e-09</v>
+        <v>1.941276379634753e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.796984386359936e-09</v>
+        <v>1.796984386359934e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.342892726015161e-09</v>
+        <v>2.342892726014981e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.190501375877002e-09</v>
+        <v>2.190501375876739e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.297591747473935e-09</v>
+        <v>2.297591747473926e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.858272457900981e-09</v>
+        <v>1.858272457900574e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.872489927019755e-09</v>
+        <v>1.872489927019742e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.840569207994822e-09</v>
+        <v>1.840569207994094e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.600694115558455e-09</v>
+        <v>1.600694115558167e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.917796674450683e-09</v>
+        <v>1.917796674450485e-09</v>
       </c>
       <c r="V7" t="n">
         <v>1.983713103104486e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.216254003618185e-09</v>
+        <v>2.216254003617825e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.540716597416329e-09</v>
+        <v>1.540716597415714e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.940008455349189e-09</v>
+        <v>2.940008455348946e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.709474872574417e-09</v>
+        <v>1.709474872574011e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.33213904832328e-09</v>
+        <v>2.332139048323176e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.960949507347427e-09</v>
+        <v>2.960949507347421e-09</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>7.305958386607315e-09</v>
+        <v>7.305958386607908e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.665695464646121e-09</v>
+        <v>1.665695464646229e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.215696039662554e-09</v>
+        <v>5.215696039662494e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.731432314338632e-09</v>
+        <v>2.731432314339188e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>2.750008402830759e-09</v>
+        <v>2.750008402830789e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.445946661620013e-09</v>
+        <v>9.445946661619961e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.102145383779927e-09</v>
+        <v>2.102145383779929e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.287570014637917e-09</v>
+        <v>2.287570014637881e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.467373930193274e-09</v>
+        <v>7.467373930193196e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>3.121965009629601e-09</v>
+        <v>3.121965009629635e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.170981488823591e-08</v>
+        <v>1.170981488823876e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.668138136385955e-08</v>
+        <v>1.668138136385954e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.93499773171265e-09</v>
+        <v>2.934997731712632e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>4.559989208223785e-09</v>
+        <v>4.559989208223737e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>7.01512952335653e-09</v>
+        <v>7.015129523356567e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.130582744409647e-09</v>
+        <v>3.130582744409684e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.176398603222649e-09</v>
+        <v>2.176398603222625e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.518965502940564e-09</v>
+        <v>7.518965502940779e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>3.004676485415753e-09</v>
+        <v>3.004676485415774e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.377918472959917e-08</v>
+        <v>1.377918472959912e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>3.14440949082053e-09</v>
+        <v>3.144409490820462e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.240088669457408e-09</v>
+        <v>4.240088669457405e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>6.539998733511408e-09</v>
+        <v>6.539998733511354e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>6.251911275794939e-09</v>
+        <v>6.251911275794905e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.581672242570604e-09</v>
+        <v>4.581672242570731e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.787339779233997e-09</v>
+        <v>3.78733977923416e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.427684460541451e-08</v>
+        <v>2.427684460541464e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.385417187264264e-09</v>
+        <v>3.385417187264115e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.126239228378611e-09</v>
+        <v>5.126239228378477e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.101661191996504e-09</v>
+        <v>4.101661191996497e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.619883447729176e-09</v>
+        <v>3.61988344772918e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.434462592064233e-09</v>
+        <v>5.434462592064171e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.048492274986428e-09</v>
+        <v>5.048492274986409e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.074504820318443e-09</v>
+        <v>5.074504820318452e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.76698834112753e-09</v>
+        <v>3.766988341127484e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.128516346376329e-09</v>
+        <v>4.128516346376124e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.039897096534559e-09</v>
+        <v>4.03989709653449e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05189168382048e-09</v>
+        <v>3.051891683820339e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.254107261047243e-09</v>
+        <v>4.254107261047096e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.533370502973993e-09</v>
+        <v>4.533370502974081e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.082884403266537e-09</v>
+        <v>5.082884403266494e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.207437358032239e-09</v>
+        <v>3.207437358032183e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.769809211311378e-09</v>
+        <v>6.769809211311232e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.353892057819384e-09</v>
+        <v>3.353892057819233e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.082550867625334e-09</v>
+        <v>5.082550867625298e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.90776111126283e-09</v>
+        <v>6.90776111126282e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.558732675283954e-09</v>
+        <v>6.558732675284021e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.530687537813546e-09</v>
+        <v>4.530687537813476e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>5.796856594922298e-09</v>
+        <v>5.79685659492225e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.842299930278707e-09</v>
+        <v>4.842299930278802e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.879123233862175e-09</v>
+        <v>4.879123233862154e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.338733272515051e-09</v>
+        <v>7.338733272515023e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.662003942010772e-09</v>
+        <v>4.662003942010745e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.729589042592562e-09</v>
+        <v>4.729589042592528e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.446894990044836e-09</v>
+        <v>6.44689499004476e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>5.033716220306327e-09</v>
+        <v>5.033716220306316e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>8.163886657433674e-09</v>
+        <v>8.163886657434147e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>9.970850901172498e-09</v>
+        <v>9.970850901172476e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.965568842986219e-09</v>
+        <v>4.965568842986217e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.557859154561222e-09</v>
+        <v>5.557859154561183e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.452728969713983e-09</v>
+        <v>6.452728969713947e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.036857283439097e-09</v>
+        <v>5.036857283439172e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.689068368572325e-09</v>
+        <v>4.689068368572272e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.636371267931581e-09</v>
+        <v>6.636371267931587e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.990965930501763e-09</v>
+        <v>4.990965930501734e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>8.918147664843069e-09</v>
+        <v>8.918147664843026e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.993465835200526e-09</v>
+        <v>3.993465835200647e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.441259164642658e-09</v>
+        <v>5.441259164642639e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>6.279549376082846e-09</v>
+        <v>6.279549376083119e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.174544880638918e-09</v>
+        <v>6.174544880638894e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.565762365965595e-09</v>
+        <v>5.565762365965528e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.27623751060211e-09</v>
+        <v>5.276237510602142e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.277772998982306e-08</v>
+        <v>1.277772998982308e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.129741445442499e-09</v>
+        <v>5.129741445442463e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.792015103937551e-09</v>
+        <v>5.792015103937298e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.341732266145167e-09</v>
+        <v>5.341732266145175e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.196182473139166e-09</v>
+        <v>5.196182473139144e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.87659443438615e-09</v>
+        <v>5.876594434386028e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.565241030664392e-09</v>
+        <v>5.565241030664356e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.74028069587737e-09</v>
+        <v>5.740280695877342e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.268819650390955e-09</v>
+        <v>5.268819650390889e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.40059236302797e-09</v>
+        <v>5.400592363027845e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.368291687080422e-09</v>
+        <v>5.368291687080282e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.008175315891432e-09</v>
+        <v>5.008175315891366e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.446368776662537e-09</v>
+        <v>5.446368776662437e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.499725814126801e-09</v>
+        <v>4.499725814126821e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.748448313008921e-09</v>
+        <v>5.748448313008865e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.064869887632103e-09</v>
+        <v>5.064869887632061e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.363312596670065e-09</v>
+        <v>6.363312596669891e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.118250905946609e-09</v>
+        <v>5.118250905946516e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.748326743184283e-09</v>
+        <v>5.748326743184107e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.446903014280574e-09</v>
+        <v>6.446903014280573e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.233849562607267e-09</v>
+        <v>3.233849562607348e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.205804425136859e-09</v>
+        <v>1.205804425136854e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.471973482245608e-09</v>
+        <v>2.471973482245504e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.517416817602023e-09</v>
+        <v>1.517416817602166e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.554240121185494e-09</v>
+        <v>1.554240121185512e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.8969459780034e-09</v>
+        <v>3.896945978003338e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.337120829334088e-09</v>
+        <v>1.337120829333967e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.404705929915879e-09</v>
+        <v>1.404705929915763e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.158250758888105e-09</v>
+        <v>3.158250758888031e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.708833107629637e-09</v>
+        <v>1.708833107629554e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.839003544756976e-09</v>
+        <v>4.839003544757066e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>6.645967788495815e-09</v>
+        <v>6.645967788495834e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.640685730309533e-09</v>
+        <v>1.640685730309442e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>2.116071860049571e-09</v>
+        <v>2.116071860049533e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>3.010941675202328e-09</v>
+        <v>3.010941675202264e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.711974170762416e-09</v>
+        <v>1.711974170762328e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.364185255895635e-09</v>
+        <v>1.364185255895509e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.311488155254895e-09</v>
+        <v>3.311488155254831e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.666082817825078e-09</v>
+        <v>1.666082817824993e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>5.476360370331412e-09</v>
+        <v>5.47636037033137e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.551744731157798e-09</v>
+        <v>1.551744731157685e-09</v>
       </c>
       <c r="W6" t="n">
         <v>1.999471870131007e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.837762081571195e-09</v>
+        <v>2.837762081571331e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.849661767962232e-09</v>
+        <v>2.849661767962131e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.240879253288904e-09</v>
+        <v>2.240879253289072e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.951354397925424e-09</v>
+        <v>1.951354397925391e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.452846877146374e-09</v>
+        <v>9.4528468771464e-09</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.804858332765816e-09</v>
+        <v>1.804858332765658e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.467131991260861e-09</v>
+        <v>2.4671319912605e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.423443630507529e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.016849153468483e-09</v>
+        <v>2.016849153468485e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.871299360462477e-09</v>
+        <v>1.871299360462488e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.434807139874501e-09</v>
+        <v>2.434807139874416e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.42344363050753e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.42344363050753e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.276596799507659e-09</v>
+        <v>2.276596799507627e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.423443630507529e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.42344363050753e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.415397583200682e-09</v>
+        <v>2.4153975832007e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.943936537714268e-09</v>
+        <v>1.943936537714138e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.958805068516323e-09</v>
+        <v>1.958805068516192e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.92650439256877e-09</v>
+        <v>1.926504392568644e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.683292203214752e-09</v>
+        <v>1.683292203214575e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.42344363050753e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.423443630507529e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.42344363050753e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.004581482150886e-09</v>
+        <v>2.004581482150827e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.05800471008407e-09</v>
+        <v>2.05800471008417e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.306661018497265e-09</v>
+        <v>2.306661018497249e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.623082593120456e-09</v>
+        <v>1.623082593120447e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.038429483993379e-09</v>
+        <v>3.038429483993259e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.793367793269924e-09</v>
+        <v>1.793367793269807e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.423443630507595e-09</v>
+        <v>2.423443630507529e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.122019901603889e-09</v>
+        <v>3.12201990160389e-09</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.226302964049154e-09</v>
+        <v>6.226302964049135e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.757862160480923e-09</v>
+        <v>1.757862160480924e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.947237991568464e-09</v>
+        <v>5.947237991568427e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.53928817864731e-09</v>
+        <v>2.539288178647308e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>3.229127373017666e-09</v>
+        <v>3.22912737301767e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.978936671781998e-09</v>
+        <v>8.978936671781971e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.044580432276596e-09</v>
+        <v>2.044580432276552e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>3.756069689391886e-09</v>
+        <v>3.756069689391834e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>7.283547119220361e-09</v>
+        <v>7.283547119220273e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>4.215409381482553e-09</v>
+        <v>4.21540938148251e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.052433142047887e-08</v>
+        <v>1.052433142047881e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.481167145550456e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.670554866402668e-09</v>
+        <v>2.670554866402612e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>4.033522950726533e-09</v>
+        <v>4.033522950726494e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.967380835530322e-09</v>
+        <v>6.967380835530286e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.226377864919876e-09</v>
+        <v>3.226377864919857e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.029499456038655e-09</v>
+        <v>2.029499456038615e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>7.124663641543132e-09</v>
+        <v>7.124663641543086e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>3.053290896124415e-09</v>
+        <v>3.053290896124373e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.075355457996046e-08</v>
+        <v>1.075355457996042e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>3.991231717893427e-09</v>
+        <v>3.991231717893532e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.270079264909482e-09</v>
+        <v>4.270079264909428e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>8.288695974667268e-09</v>
+        <v>8.288695974667213e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.043345257998446e-08</v>
+        <v>1.043345257998441e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.671500189697939e-09</v>
+        <v>4.671500189697885e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.798499526563229e-09</v>
+        <v>3.798499526563176e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.266713472739193e-08</v>
+        <v>2.266713472739195e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.394688471808568e-09</v>
+        <v>3.394688471808576e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.140951226380289e-09</v>
+        <v>5.140951226380294e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="E3" t="n">
         <v>4.113124404898218e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.631605608364178e-09</v>
+        <v>3.631605608364177e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.450271360956926e-09</v>
+        <v>5.450271360956951e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.063545455745158e-09</v>
+        <v>5.063545455745236e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.08390619888444e-09</v>
+        <v>5.083906198884435e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.777477029365731e-09</v>
+        <v>3.777477029365773e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.140158490593536e-09</v>
+        <v>4.140158490593621e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.051256500820068e-09</v>
+        <v>4.051256500820098e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.060098854435509e-09</v>
+        <v>3.060098854435583e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.266217975804385e-09</v>
+        <v>4.266217975804553e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.548224848314419e-09</v>
+        <v>4.548224848314548e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.0975714610901e-09</v>
+        <v>5.097571461090158e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.21614079749753e-09</v>
+        <v>3.2161407974976e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.789994516805602e-09</v>
+        <v>6.789994516805528e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.363062761361799e-09</v>
+        <v>3.363062761361781e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.097236861305347e-09</v>
+        <v>5.09723686130534e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.92240627125095e-09</v>
+        <v>6.922406271250934e-09</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.152471172867541e-09</v>
+        <v>6.152471172867529e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.551557963373123e-09</v>
+        <v>4.551557963373139e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>6.050755267344687e-09</v>
+        <v>6.050755267344659e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.759310045440922e-09</v>
+        <v>4.759310045440961e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>5.042038169169866e-09</v>
+        <v>5.042038169169904e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.155773836279274e-09</v>
+        <v>7.155773836279217e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.628282414301594e-09</v>
+        <v>4.628282414301554e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>5.252100151198589e-09</v>
+        <v>5.252100151198546e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.379510645151109e-09</v>
+        <v>6.379510645151168e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>5.419524075126623e-09</v>
+        <v>5.419524075126604e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.719052075237914e-09</v>
+        <v>7.719052075237885e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>9.273265381011245e-09</v>
+        <v>9.273265381011263e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.856442744977633e-09</v>
+        <v>4.856442744977587e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>5.353228606934407e-09</v>
+        <v>5.353228606934345e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.422585354846706e-09</v>
+        <v>6.42258535484668e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.059033701133956e-09</v>
+        <v>5.059033701133945e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.622785575552605e-09</v>
+        <v>4.622785575552589e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.479913090730437e-09</v>
+        <v>6.479913090730389e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.99594553349783e-09</v>
+        <v>4.995945533497796e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.802601225194734e-09</v>
+        <v>7.802601225194695e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>4.371276528863792e-09</v>
+        <v>4.371276528864056e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.439450605669629e-09</v>
+        <v>5.439450605669547e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>6.904189207396404e-09</v>
+        <v>6.904189207396375e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.685927805030956e-09</v>
+        <v>7.685927805030893e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.585763819032492e-09</v>
+        <v>5.585763819032457e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.267565328611234e-09</v>
+        <v>5.267565328611194e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.217464938388424e-08</v>
+        <v>1.217464938388428e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2902,85 +2902,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.120380940941991e-09</v>
+        <v>5.120380940941955e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.784654201655941e-09</v>
+        <v>5.784654201655953e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.332954868991375e-09</v>
+        <v>5.332954868991383e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.188736759815622e-09</v>
+        <v>5.188736759815653e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.8696167661636e-09</v>
+        <v>5.869616766163682e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.570346107390142e-09</v>
+        <v>5.570346107390153e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.72760917416005e-09</v>
+        <v>5.727609174160076e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.259902875241395e-09</v>
+        <v>5.259902875241479e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.392096009038224e-09</v>
+        <v>5.392096009038268e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.359692277705618e-09</v>
+        <v>5.359692277705617e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.998426954359133e-09</v>
+        <v>4.998426954359148e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.438043211132301e-09</v>
+        <v>5.438043211132358e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.574293984358686e-09</v>
+        <v>4.574293984358575e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.741061794273461e-09</v>
+        <v>5.741061794273554e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.055302410268272e-09</v>
+        <v>5.055302410268351e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.357930124646855e-09</v>
+        <v>6.357930124646824e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.10885374085198e-09</v>
+        <v>5.108853740851985e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.74093983658098e-09</v>
+        <v>5.740939836581077e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.435880745556812e-09</v>
+        <v>6.435880745556819e-09</v>
       </c>
     </row>
     <row r="6">
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.840708829148391e-09</v>
+        <v>2.84070882914834e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.239795619653965e-09</v>
+        <v>1.239795619653966e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.738992923625534e-09</v>
+        <v>2.738992923625489e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.447547701721787e-09</v>
+        <v>1.447547701721788e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.730275825450726e-09</v>
+        <v>1.73027582545073e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.727202570866385e-09</v>
+        <v>3.727202570866322e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.316520070582433e-09</v>
+        <v>1.316520070582381e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.940337807479429e-09</v>
+        <v>1.940337807479369e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>3.091958011808398e-09</v>
+        <v>3.091958011808477e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.107761731407486e-09</v>
+        <v>2.107761731407436e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.407289731518766e-09</v>
+        <v>4.407289731518716e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.961503037292097e-09</v>
+        <v>5.961503037292104e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.544680401258463e-09</v>
+        <v>1.544680401258411e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.924657341521515e-09</v>
+        <v>1.924657341521442e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.994014089433852e-09</v>
+        <v>2.994014089433777e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.74727135741482e-09</v>
+        <v>1.747271357414772e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.311023231833479e-09</v>
+        <v>1.311023231833416e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.168150747011271e-09</v>
+        <v>3.168150747011212e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.684183189778683e-09</v>
+        <v>1.684183189778621e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.374029959781839e-09</v>
+        <v>4.374029959781788e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.861882475165037e-09</v>
+        <v>1.861882475165164e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.010879340256703e-09</v>
+        <v>2.010879340256633e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>3.475617941983538e-09</v>
+        <v>3.475617941983465e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>4.374165461311771e-09</v>
+        <v>4.374165461311717e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.274001475313346e-09</v>
+        <v>2.274001475313269e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.955802984892072e-09</v>
+        <v>1.955802984892022e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.862887040165105e-09</v>
+        <v>8.862887040165103e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.80861859722283e-09</v>
+        <v>1.808618597222777e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.472891857936778e-09</v>
+        <v>2.472891857936781e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="E7" t="n">
         <v>2.021192525272213e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.876974416096478e-09</v>
+        <v>1.876974416096479e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.441045500750694e-09</v>
+        <v>2.441045500750779e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.282793474047447e-09</v>
+        <v>2.282793474047456e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.415846830440898e-09</v>
+        <v>2.4158468304409e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.948140531522218e-09</v>
+        <v>1.948140531522301e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.963524743625325e-09</v>
+        <v>1.96352474362537e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.931121012292737e-09</v>
+        <v>1.93112101229271e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.68666461064001e-09</v>
+        <v>1.68666461063998e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.009471945719435e-09</v>
+        <v>2.009471945719455e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.064899930659925e-09</v>
+        <v>2.064899930659967e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.312490528860589e-09</v>
+        <v>2.312490528860655e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.626731144855383e-09</v>
+        <v>1.626731144855445e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.046167780927715e-09</v>
+        <v>3.046167780927648e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.797091397132808e-09</v>
+        <v>1.797091397132814e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.429177492861826e-09</v>
+        <v>2.4291774928619e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.124118401837654e-09</v>
+        <v>3.124118401837645e-09</v>
       </c>
     </row>
   </sheetData>
@@ -3322,82 +3322,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>5.521141322507563e-09</v>
+        <v>5.521141322507453e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.824591362160235e-09</v>
+        <v>1.824591362160231e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>5.062572920160442e-09</v>
+        <v>5.062572920160339e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.105303804055529e-09</v>
+        <v>2.105303804055528e-09</v>
       </c>
       <c r="F2" t="n">
         <v>3.557666717537045e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>8.075591757662912e-09</v>
+        <v>8.075591757662937e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.126263282971005e-09</v>
+        <v>2.126263282970891e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>3.737844684249664e-09</v>
+        <v>3.737844684249547e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.848627164264133e-09</v>
+        <v>6.848627164264055e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>4.614534042532642e-09</v>
+        <v>4.614534042532542e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>8.940528234521755e-09</v>
+        <v>8.94052823452169e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>1.268955034027378e-08</v>
+        <v>1.268955034027384e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.431650123397119e-09</v>
+        <v>2.431650123397007e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.18370741418493e-09</v>
+        <v>3.183707414184809e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>6.504458020709868e-09</v>
+        <v>6.504458020709815e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.366819351234676e-09</v>
+        <v>3.366819351234564e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.482157672460088e-09</v>
+        <v>2.482157672459975e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>6.679971901420873e-09</v>
+        <v>6.67997190142079e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>3.333402492019988e-09</v>
+        <v>3.333402492019884e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.086004853019694e-08</v>
+        <v>1.086004853019682e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.771548994698162e-09</v>
+        <v>5.771548994698118e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>4.467401233589006e-09</v>
+        <v>4.467401233588891e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>8.972923399076961e-09</v>
+        <v>8.972923399076887e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.550600082264063e-08</v>
+        <v>1.550600082264059e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>4.471425658596347e-09</v>
+        <v>4.4714256585963e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>4.089374344130988e-09</v>
+        <v>4.089374344130874e-09</v>
       </c>
       <c r="AB2" t="n">
         <v>2.06740908298354e-08</v>
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.397754162611109e-09</v>
+        <v>3.397754162611069e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.148318616172423e-09</v>
+        <v>5.148318616172422e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.118167160048958e-09</v>
+        <v>4.118167160048954e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.637654435285662e-09</v>
+        <v>3.637654435285659e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.456947440376612e-09</v>
+        <v>5.456947440376493e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.071253403358152e-09</v>
+        <v>5.071253403358139e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.085296600719762e-09</v>
+        <v>5.085296600719817e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.781215043068641e-09</v>
+        <v>3.78121504306861e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.144533511456338e-09</v>
+        <v>4.144533511456196e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.055475375835813e-09</v>
+        <v>4.05547537583568e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.062576878084505e-09</v>
+        <v>3.062576878084465e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.270971014470459e-09</v>
+        <v>4.270971014470353e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.558311263780084e-09</v>
+        <v>4.558311263780033e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.103628064781738e-09</v>
+        <v>5.103628064781652e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.218892890392796e-09</v>
+        <v>3.218892890392771e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.799291574532124e-09</v>
+        <v>6.799291574532044e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.366072905338468e-09</v>
+        <v>3.366072905338359e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.103292877313588e-09</v>
+        <v>5.103292877313482e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.926020275172414e-09</v>
+        <v>6.926020275172409e-09</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.849797231748243e-09</v>
+        <v>5.84979723174817e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.531062564046559e-09</v>
+        <v>4.53106256404654e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>5.682654433874773e-09</v>
+        <v>5.682654433874687e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.555844994530998e-09</v>
+        <v>4.555844994530988e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>5.117735859123053e-09</v>
+        <v>5.117735859123032e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>6.780864419490917e-09</v>
+        <v>6.780864419490903e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.612404051007786e-09</v>
+        <v>4.612404051007714e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>5.199806547629595e-09</v>
+        <v>5.19980654762953e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.203070339398778e-09</v>
+        <v>6.203070339398725e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>5.519349524117566e-09</v>
+        <v>5.519349524117482e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.096123608709055e-09</v>
+        <v>7.096123608709027e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>8.45116129791716e-09</v>
+        <v>8.4511612979172e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.723713968309772e-09</v>
+        <v>4.723713968309701e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.997830019699363e-09</v>
+        <v>4.997830019699283e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>6.208204621555338e-09</v>
+        <v>6.208204621555286e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.064572170545067e-09</v>
+        <v>5.064572170544995e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.74212337685364e-09</v>
+        <v>4.742123376853569e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>6.272177370086505e-09</v>
+        <v>6.272177370086396e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>5.052392117761902e-09</v>
+        <v>5.052392117761816e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.795766216337385e-09</v>
+        <v>7.795766216337301e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>5.155529686032883e-09</v>
+        <v>5.15552968603318e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.465721342978257e-09</v>
+        <v>5.465721342978195e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>7.107931265786219e-09</v>
+        <v>7.107931265786166e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.489161271406891e-09</v>
+        <v>9.489161271406834e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.467188198636312e-09</v>
+        <v>5.46718819863621e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.327934980786667e-09</v>
+        <v>5.327934980786598e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.139902044326653e-08</v>
+        <v>1.13990204432665e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.07584754603693e-09</v>
+        <v>5.075847546036833e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.742522118958085e-09</v>
+        <v>5.74252211895807e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.289510051555741e-09</v>
+        <v>5.28951005155572e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.146890442979209e-09</v>
+        <v>5.146890442979199e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.826399315514179e-09</v>
+        <v>5.826399315514056e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.555238474524989e-09</v>
+        <v>5.555238474524969e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.679500103505391e-09</v>
+        <v>5.679500103505416e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.215614534138714e-09</v>
+        <v>5.21561453413861e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.348039849565112e-09</v>
+        <v>5.348039849565033e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.315579204904844e-09</v>
+        <v>5.315579204904782e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.953679361677407e-09</v>
+        <v>4.953679361677276e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.394124834709687e-09</v>
+        <v>5.394124834709572e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.713318779669943e-09</v>
+        <v>4.713318779670248e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.697618551995412e-09</v>
+        <v>5.697618551995312e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.010654712608413e-09</v>
+        <v>5.010654712608358e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.315667989813165e-09</v>
+        <v>6.315667989813113e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.064300099781132e-09</v>
+        <v>5.064300099781038e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.697496380099198e-09</v>
+        <v>5.697496380099134e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.38801016408696e-09</v>
+        <v>6.388010164086943e-09</v>
       </c>
     </row>
     <row r="6">
@@ -3674,85 +3674,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.58271249407629e-09</v>
+        <v>2.582712494076195e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.263977826374576e-09</v>
+        <v>1.263977826374575e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>2.415569696202807e-09</v>
+        <v>2.415569696202719e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.288760256859014e-09</v>
+        <v>1.288760256859015e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.850651121451064e-09</v>
+        <v>1.850651121451061e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.396901334259973e-09</v>
+        <v>3.39690133425977e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.345319313335838e-09</v>
+        <v>1.345319313335742e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.932721809957653e-09</v>
+        <v>1.932721809957559e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.933448837975099e-09</v>
+        <v>2.933448837975035e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>2.252264786445593e-09</v>
+        <v>2.252264786445512e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>3.829038871037134e-09</v>
+        <v>3.829038871037058e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>5.184076560245175e-09</v>
+        <v>5.184076560245165e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.45662923063782e-09</v>
+        <v>1.45662923063773e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.61386693446826e-09</v>
+        <v>1.613866934468146e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.824241536324244e-09</v>
+        <v>2.824241536324148e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.79748743287311e-09</v>
+        <v>1.797487432873023e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.475038639181692e-09</v>
+        <v>1.475038639181595e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>3.005092632414559e-09</v>
+        <v>3.005092632414427e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.785307380089948e-09</v>
+        <v>1.785307380089846e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.411803131106283e-09</v>
+        <v>4.411803131106163e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>2.512730094360097e-09</v>
+        <v>2.512730094360058e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>2.081758257747173e-09</v>
+        <v>2.081758257747058e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>3.723968180555066e-09</v>
+        <v>3.723968180555026e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>6.222076533734926e-09</v>
+        <v>6.222076533734865e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.20010346096435e-09</v>
+        <v>2.20010346096424e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.060850243114719e-09</v>
+        <v>2.060850243114628e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.131935705594529e-09</v>
+        <v>8.131935705594531e-09</v>
       </c>
     </row>
     <row r="7">
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.808762808364903e-09</v>
+        <v>1.808762808364863e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.475437381286104e-09</v>
+        <v>2.4754373812861e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.022425313883757e-09</v>
+        <v>2.022425313883751e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.879805705307234e-09</v>
+        <v>1.879805705307229e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.442436230282983e-09</v>
+        <v>2.442436230282921e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.285616973101258e-09</v>
+        <v>2.285616973101238e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.412415365833394e-09</v>
+        <v>2.412415365833379e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.948529796466679e-09</v>
+        <v>1.948529796466638e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.964076764333994e-09</v>
+        <v>1.964076764333901e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.931616119673735e-09</v>
+        <v>1.931616119673648e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.686594624005377e-09</v>
+        <v>1.686594624005304e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>2.010161749478601e-09</v>
+        <v>2.010161749478439e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.070519187997116e-09</v>
+        <v>2.070519187997132e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.313655466764242e-09</v>
+        <v>2.313655466764175e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.62669162737732e-09</v>
+        <v>1.626691627377227e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.048583252141247e-09</v>
+        <v>3.048583252141141e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.797215362109176e-09</v>
+        <v>1.797215362109067e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.430411642427288e-09</v>
+        <v>2.430411642427165e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.120925426414976e-09</v>
+        <v>3.120925426414971e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.24405630356829e-09</v>
+        <v>2.244056303568288e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.457717566665165e-09</v>
+        <v>1.457717566665155e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.333326510853554e-09</v>
+        <v>2.333326510853559e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.370608997270224e-09</v>
+        <v>1.37060899727022e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.74226613397136e-09</v>
+        <v>1.742266133971359e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>3.734938386761062e-09</v>
+        <v>3.73493838676107e-09</v>
       </c>
       <c r="H2" t="n">
         <v>2.564864544012473e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>1.851322265094658e-09</v>
+        <v>1.851322265094661e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>3.196474936927337e-09</v>
+        <v>3.196474936927334e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>2.373750937828707e-09</v>
+        <v>2.373750937828712e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>4.339414881324017e-09</v>
+        <v>4.339414881324016e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>6.280583115330502e-09</v>
+        <v>6.280583115330503e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.16972002266523e-09</v>
+        <v>2.169720022665226e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.936666021561563e-09</v>
+        <v>1.936666021561564e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>2.901795573076173e-09</v>
+        <v>2.901795573076184e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.096043757715957e-09</v>
+        <v>2.096043757715959e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.057931868708765e-09</v>
+        <v>2.05793186870877e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7671879029085e-09</v>
+        <v>2.767187902908508e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.90845325829562e-09</v>
+        <v>1.908453258295622e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>5.597306932464043e-09</v>
+        <v>5.597306932464059e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>1.892122067701965e-09</v>
+        <v>1.892122067701958e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>3.442091863068808e-09</v>
+        <v>3.442091863068815e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>3.066771002284258e-09</v>
+        <v>3.066771002284269e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.214972161887625e-09</v>
+        <v>2.214972161887612e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.650862300954149e-09</v>
+        <v>2.650862300954151e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.587266652517104e-09</v>
+        <v>2.587266652517097e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.629642435515808e-09</v>
+        <v>6.629642435515798e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.281944523436477e-09</v>
+        <v>3.281944523436488e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.004655886173067e-09</v>
+        <v>5.004655886173063e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.994830387857375e-09</v>
+        <v>3.994830387857374e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.520157086157118e-09</v>
+        <v>3.520157086157105e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.298496426995952e-09</v>
+        <v>5.298496426995962e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.921301132720967e-09</v>
+        <v>4.921301132720965e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.925750874486945e-09</v>
+        <v>4.925750874486947e-09</v>
       </c>
       <c r="N3" t="n">
         <v>3.657464770507476e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.013259710665267e-09</v>
+        <v>4.013259710665266e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.926045773607336e-09</v>
+        <v>3.926045773607344e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.953708024975361e-09</v>
+        <v>2.953708024975359e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.137003323648366e-09</v>
+        <v>4.137003323648364e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.42077268646394e-09</v>
+        <v>4.420772686463914e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.952493520376983e-09</v>
+        <v>4.952493520376997e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.106787075686966e-09</v>
+        <v>3.106787075686959e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.612914150050814e-09</v>
+        <v>6.612914150050806e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.250919315481341e-09</v>
+        <v>3.250919315481346e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.952165273893872e-09</v>
+        <v>4.952165273893896e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.699164403199437e-09</v>
+        <v>6.699164403199416e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.326768881797991e-09</v>
+        <v>4.326768881797989e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.073516046331752e-09</v>
+        <v>4.073516046331756e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.359306824089775e-09</v>
+        <v>4.359306824089776e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.965198131942272e-09</v>
+        <v>3.965198131942271e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.129898428127024e-09</v>
+        <v>4.129898428127023e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>4.87017789430045e-09</v>
+        <v>4.870177894300446e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.44369971831934e-09</v>
+        <v>4.443699718319362e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.183621936490261e-09</v>
+        <v>4.183621936490297e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>4.538641462748814e-09</v>
+        <v>4.538641462748825e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.374041053034625e-09</v>
+        <v>4.374041053034633e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>5.090502478447277e-09</v>
+        <v>5.090502478447282e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>5.781248844397768e-09</v>
+        <v>5.781248844397769e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.299674180309502e-09</v>
+        <v>4.299674180309509e-09</v>
       </c>
       <c r="O4" t="n">
         <v>4.214728733565465e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.566507121969169e-09</v>
+        <v>4.566507121969175e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.272820046885871e-09</v>
+        <v>4.272820046885879e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.258928710875149e-09</v>
+        <v>4.258928710875154e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>4.517444206836109e-09</v>
+        <v>4.517444206836119e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.204445512646022e-09</v>
+        <v>4.204445512646016e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>5.548989360173604e-09</v>
+        <v>5.548989360173611e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.379217626665024e-09</v>
+        <v>3.379217626665012e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>4.763438775192136e-09</v>
+        <v>4.763438775192122e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>4.626638728676211e-09</v>
+        <v>4.626638728676224e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.316168053678615e-09</v>
+        <v>4.316168053678625e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.475044890887934e-09</v>
+        <v>4.475044890887938e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.451865023810436e-09</v>
+        <v>4.451865023810444e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.926734035314309e-09</v>
+        <v>5.926734035314294e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.705066950441148e-09</v>
+        <v>4.705066950441172e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.366333413539804e-09</v>
+        <v>5.366333413539806e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.921696013647931e-09</v>
+        <v>4.92169601364793e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.777918803149133e-09</v>
+        <v>4.77791880314913e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.440076439740593e-09</v>
+        <v>5.440076439740606e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.167320357183822e-09</v>
+        <v>5.16732035718381e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="M5" t="n">
         <v>5.287428401853684e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>4.841939670917153e-09</v>
+        <v>4.841939670917151e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>4.971622748649539e-09</v>
+        <v>4.971622748649563e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>4.93983429270968e-09</v>
+        <v>4.939834292709687e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.585428601099628e-09</v>
+        <v>4.585428601099631e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.016725842511016e-09</v>
+        <v>5.016725842511018e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.300881084289068e-09</v>
+        <v>4.300881084289073e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.313962443249238e-09</v>
+        <v>5.313962443249247e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.641224117539049e-09</v>
+        <v>4.641224117539032e-09</v>
       </c>
       <c r="Y5" t="n">
         <v>5.919166265121925e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.693758626457879e-09</v>
+        <v>4.693758626457903e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.313842801260612e-09</v>
+        <v>5.313842801260609e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.952073976166829e-09</v>
+        <v>5.952073976166848e-09</v>
       </c>
     </row>
     <row r="6">
@@ -4358,49 +4358,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349354360129964e-09</v>
+        <v>1.349354360129954e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.096101524663729e-09</v>
+        <v>1.09610152466372e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.38189230242175e-09</v>
+        <v>1.381892302421741e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.87783610274247e-10</v>
+        <v>9.877836102742433e-10</v>
       </c>
       <c r="F6" t="n">
         <v>1.152483906458999e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.776510583749346e-09</v>
+        <v>1.776510583749335e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.466285196651316e-09</v>
+        <v>1.466285196651334e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.206207414822241e-09</v>
+        <v>1.206207414822268e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.564724679671058e-09</v>
+        <v>1.564724679671068e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.396626531366601e-09</v>
+        <v>1.396626531366604e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.11308795677926e-09</v>
+        <v>2.11308795677925e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>2.80383432272974e-09</v>
+        <v>2.803834322729739e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32225965864148e-09</v>
+        <v>1.322259658641475e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.121061423014357e-09</v>
+        <v>1.121061423014354e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.472839811418064e-09</v>
+        <v>1.472839811418062e-09</v>
       </c>
       <c r="Q6" t="n">
         <v>1.295405525217852e-09</v>
@@ -4409,34 +4409,34 @@
         <v>1.281514189207126e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.540029685168087e-09</v>
+        <v>1.54002968516809e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.227030990978e-09</v>
+        <v>1.227030990977991e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>2.455322049622497e-09</v>
+        <v>2.455322049622492e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.062953964285583e-09</v>
+        <v>1.062953964285593e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.669771464641026e-09</v>
+        <v>1.669771464641008e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>1.532971418125107e-09</v>
+        <v>1.53297141812511e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.338753532010591e-09</v>
+        <v>1.33875353201059e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.49763036921991e-09</v>
+        <v>1.497630369219901e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.474450502142414e-09</v>
+        <v>1.474450502142403e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.949319513646283e-09</v>
+        <v>2.949319513646271e-09</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.727652428773126e-09</v>
+        <v>1.727652428773141e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.388918891871778e-09</v>
+        <v>2.388918891871775e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.944281491979907e-09</v>
+        <v>1.944281491979897e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.800504281481109e-09</v>
+        <v>1.800504281481105e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.346409129189485e-09</v>
+        <v>2.3464091291895e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.193403574106072e-09</v>
+        <v>2.193403574106061e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.31001388018566e-09</v>
+        <v>2.310013880185658e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.864525149249128e-09</v>
+        <v>1.864525149249116e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.877955438098435e-09</v>
+        <v>1.877955438098446e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.846166982158573e-09</v>
+        <v>1.846166982158582e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.608014079431605e-09</v>
+        <v>1.608014079431612e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.923058531959908e-09</v>
+        <v>1.923058531959895e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.984617421909629e-09</v>
+        <v>1.984617421909621e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.220295132698133e-09</v>
+        <v>2.220295132698124e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.54755680698794e-09</v>
+        <v>1.547556806987916e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.941751743453897e-09</v>
+        <v>2.94175174345391e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.716344104789854e-09</v>
+        <v>1.71634410478987e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.336428279592589e-09</v>
+        <v>2.336428279592573e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.974659454498803e-09</v>
+        <v>2.97465945449881e-09</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.758776702779471e-09</v>
+        <v>1.758776702779344e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.665469573454807e-09</v>
+        <v>1.665469573454843e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.009275797128465e-09</v>
+        <v>2.009275797128341e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.345288509812982e-09</v>
+        <v>1.345288509812976e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.83029297926872e-09</v>
+        <v>1.830292979268716e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>2.385947395031261e-09</v>
+        <v>2.385947395030978e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.227227379175629e-09</v>
+        <v>2.227227379175502e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.115084498988218e-09</v>
+        <v>2.115084498988104e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>2.207017393762334e-09</v>
+        <v>2.207017393762248e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>2.150507776747031e-09</v>
+        <v>2.150507776746909e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.056046829506355e-09</v>
+        <v>2.05604682950623e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>2.019916178086376e-09</v>
+        <v>2.01991617808637e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.203026463226573e-09</v>
+        <v>2.203026463226463e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>2.152854850823138e-09</v>
+        <v>2.152854850823014e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.804872704016051e-09</v>
+        <v>1.804872704015929e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.774149539609973e-09</v>
+        <v>1.774149539609876e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.18491141559205e-09</v>
+        <v>2.184911415591919e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>2.102267934492428e-09</v>
+        <v>2.102267934492297e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.737476920110875e-09</v>
+        <v>1.737476920110911e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.955054382008965e-09</v>
+        <v>1.955054382008832e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>2.103343558189408e-09</v>
+        <v>2.10334355818923e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>2.747337472878203e-09</v>
+        <v>2.747337472878079e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>4.804483585811672e-09</v>
+        <v>4.804483585811559e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.483973118674873e-09</v>
+        <v>3.483973118674749e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.307945724193077e-09</v>
+        <v>2.30794572419295e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.608842774769544e-09</v>
+        <v>2.60884277476942e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.855656097773336e-09</v>
+        <v>1.855656097773327e-09</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.271254638311014e-09</v>
+        <v>3.271254638310933e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>4.996645516402862e-09</v>
+        <v>4.996645516402704e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.986582416437716e-09</v>
+        <v>3.986582416437694e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.511948708358209e-09</v>
+        <v>3.511948708358197e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.288533636970014e-09</v>
+        <v>5.288533636969998e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.911828248655656e-09</v>
+        <v>4.911828248655531e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.905721165662905e-09</v>
+        <v>4.905721165662884e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.646910284292489e-09</v>
+        <v>3.646910284292426e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.002833511134112e-09</v>
+        <v>4.002833511133951e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.915588127910202e-09</v>
+        <v>3.915588127910136e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.942899789735322e-09</v>
+        <v>2.942899789735314e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.126672198302149e-09</v>
+        <v>4.126672198302117e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.413327453376745e-09</v>
+        <v>4.41332745337663e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.942405974315904e-09</v>
+        <v>4.942405974315705e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.096034035171104e-09</v>
+        <v>3.096034035170997e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.603511607954111e-09</v>
+        <v>6.603511607953987e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.240218243797071e-09</v>
+        <v>3.240218243797042e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.942077609480339e-09</v>
+        <v>4.942077609480126e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.675099014523457e-09</v>
+        <v>6.675099014523422e-09</v>
       </c>
     </row>
     <row r="4">
@@ -4866,85 +4866,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.070507146488236e-09</v>
+        <v>4.070507146488099e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.071176339134991e-09</v>
+        <v>4.071176339134779e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.161811124869564e-09</v>
+        <v>4.161811124869437e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.877959025052894e-09</v>
+        <v>3.877959025052883e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.0841175643134e-09</v>
+        <v>4.084117564313395e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>4.299103499203869e-09</v>
+        <v>4.299103499203734e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.241251917209066e-09</v>
+        <v>4.241251917208931e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.20037715422891e-09</v>
+        <v>4.200377154228805e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>4.111936732488812e-09</v>
+        <v>4.1119367324888e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.213288523010886e-09</v>
+        <v>4.213288523010771e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>4.178858616958112e-09</v>
+        <v>4.178858616957974e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.142584471818154e-09</v>
+        <v>4.142584471818145e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.232430967527156e-09</v>
+        <v>4.23243096752701e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.214144003950903e-09</v>
+        <v>4.214144003950773e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.087308597652388e-09</v>
+        <v>4.087308597652273e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.076110364995978e-09</v>
+        <v>4.076110364996029e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.22582824538198e-09</v>
+        <v>4.225828245381846e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>4.195705666969888e-09</v>
+        <v>4.195705666969792e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.0627436258202e-09</v>
+        <v>4.062743625820162e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>4.142048055758503e-09</v>
+        <v>4.142048055758367e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.464858214122773e-09</v>
+        <v>3.464858214122585e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>4.430825938922583e-09</v>
+        <v>4.43082593892245e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>5.180631540857578e-09</v>
+        <v>5.180631540857462e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.699320981802995e-09</v>
+        <v>4.699320981802866e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.27067280612526e-09</v>
+        <v>4.270672806125137e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.38034624774882e-09</v>
+        <v>4.380346247748703e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>4.09800626571693e-09</v>
+        <v>4.09800626571692e-09</v>
       </c>
     </row>
     <row r="5">
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.62178759357687e-09</v>
+        <v>4.621787593576535e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.285350853696724e-09</v>
+        <v>5.285350853696425e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.840679638378639e-09</v>
+        <v>4.840679638378627e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.697061330567963e-09</v>
+        <v>4.697061330567952e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.357062100502079e-09</v>
+        <v>5.357062100501944e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.097808527604794e-09</v>
+        <v>5.09780852760476e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.194426502956761e-09</v>
+        <v>5.194426502956751e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>4.75870966536579e-09</v>
+        <v>4.758709665365743e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>4.888439502088008e-09</v>
+        <v>4.888439502088021e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>4.856639584389917e-09</v>
+        <v>4.856639584389889e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.502106107008329e-09</v>
+        <v>4.502106107008223e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>4.933577249373498e-09</v>
+        <v>4.933577249373406e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.306820218718125e-09</v>
+        <v>4.306820218717999e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.23090263190091e-09</v>
+        <v>5.230902631900794e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.557921741276576e-09</v>
+        <v>4.557921741276396e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.836356129674846e-09</v>
+        <v>5.836356129674734e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.610475192224282e-09</v>
+        <v>4.610475192224226e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.230782946774212e-09</v>
+        <v>5.230782946774014e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.854636616116369e-09</v>
+        <v>5.854636616116352e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5042,85 +5042,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.164788340352941e-09</v>
+        <v>1.164788340352849e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.165457532999729e-09</v>
+        <v>1.165457532999645e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.256092318734272e-09</v>
+        <v>1.256092318734175e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.722402189176291e-10</v>
+        <v>9.722402189176245e-10</v>
       </c>
       <c r="F6" t="n">
-        <v>1.178398758178137e-09</v>
+        <v>1.178398758178135e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.277423322809395e-09</v>
+        <v>1.27742332280924e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.335533111073767e-09</v>
+        <v>1.33553311107367e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.294658348093662e-09</v>
+        <v>1.294658348093553e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1970666148831e-09</v>
+        <v>1.197066614882983e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.307569716875601e-09</v>
+        <v>1.307569716875506e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.27313981082282e-09</v>
+        <v>1.273139810822731e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.236865665682895e-09</v>
+        <v>1.236865665682888e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.326712161391833e-09</v>
+        <v>1.326712161391754e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.192463827556379e-09</v>
+        <v>1.192463827556283e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.065628421257872e-09</v>
+        <v>1.065628421257763e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.170391558860692e-09</v>
+        <v>1.170391558860767e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.320109439246686e-09</v>
+        <v>1.320109439246596e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.289986860834632e-09</v>
+        <v>1.289986860834527e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.157024819684909e-09</v>
+        <v>1.157024819684906e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.120367879363987e-09</v>
+        <v>1.120367879363891e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.134287515576681e-09</v>
+        <v>1.134287515576692e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.409145762528061e-09</v>
+        <v>1.409145762527957e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.158951364463068e-09</v>
+        <v>2.15895136446297e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.793602175667702e-09</v>
+        <v>1.793602175667612e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.36495399998997e-09</v>
+        <v>1.364953999989872e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.47462744161353e-09</v>
+        <v>1.474627441613442e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.192287459581669e-09</v>
+        <v>1.192287459581662e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.716068787441592e-09</v>
+        <v>1.716068787441288e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.37963204756146e-09</v>
+        <v>2.379632047561248e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.934960832243378e-09</v>
+        <v>1.934960832243367e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7913425244327e-09</v>
+        <v>1.791342524432691e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.335381924107605e-09</v>
+        <v>2.335381924107453e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.18293840999907e-09</v>
+        <v>2.182938409998949e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.288707696821502e-09</v>
+        <v>2.288707696821492e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.852990859230538e-09</v>
+        <v>1.852990859230489e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.866759325693526e-09</v>
+        <v>1.866759325693527e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.834959407995431e-09</v>
+        <v>1.834959407995395e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.596387300873023e-09</v>
+        <v>1.596387300872965e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.911897072978987e-09</v>
+        <v>1.911897072978913e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.976249520172098e-09</v>
+        <v>1.976249520172036e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.209222455506406e-09</v>
+        <v>2.209222455506297e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.536241564882039e-09</v>
+        <v>1.536241564881903e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.930637323539604e-09</v>
+        <v>2.930637323539487e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.704756386089039e-09</v>
+        <v>1.704756386088956e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.325064140638898e-09</v>
+        <v>2.32506414063876e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.948917809981113e-09</v>
+        <v>2.948917809981099e-09</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.925333415323311e-09</v>
+        <v>1.925333415323334e-09</v>
       </c>
       <c r="C2" t="n">
         <v>1.660434394766775e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.135920902346577e-09</v>
+        <v>2.135920902346585e-09</v>
       </c>
       <c r="E2" t="n">
         <v>1.632875427833502e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.781440557692191e-09</v>
+        <v>1.78144055769219e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>2.681895323032856e-09</v>
+        <v>2.681895323032861e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.109672279910036e-09</v>
+        <v>2.109672279910207e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.111764214529233e-09</v>
+        <v>2.111764214529252e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>2.297221100884411e-09</v>
+        <v>2.297221100884521e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>2.211261157048025e-09</v>
+        <v>2.211261157048044e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>2.045722214942759e-09</v>
+        <v>2.04572221494278e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>2.15123718110877e-09</v>
+        <v>2.151237181108778e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.012523355357465e-09</v>
+        <v>2.012523355357483e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>2.216777604547506e-09</v>
+        <v>2.216777604547518e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>1.949284520761444e-09</v>
+        <v>1.949284520761547e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.80991479352609e-09</v>
+        <v>1.809914793526106e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.37387977898461e-09</v>
+        <v>2.373879778984633e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>1.943815753152373e-09</v>
+        <v>1.943815753152346e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.829463115949143e-09</v>
+        <v>1.829463115949155e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.938304060424809e-09</v>
+        <v>1.938304060424819e-09</v>
       </c>
       <c r="V2" t="n">
         <v>2.258231390009251e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>3.462673083006763e-09</v>
+        <v>3.462673083006782e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>5.65125680573114e-09</v>
+        <v>5.651256805731106e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.517112958392932e-09</v>
+        <v>3.517112958392962e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.048592218996102e-09</v>
+        <v>2.048592218996082e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.831829349120601e-09</v>
+        <v>2.83182934912064e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.107224085427573e-09</v>
+        <v>2.107224085427567e-09</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.281355760787505e-09</v>
+        <v>3.281355760787568e-09</v>
       </c>
       <c r="C3" t="n">
         <v>5.012143270775795e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>3.99992611393843e-09</v>
+        <v>3.999926113938427e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.522950503856056e-09</v>
+        <v>3.522950503856058e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.304788887473334e-09</v>
+        <v>5.304788887473378e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.927298282063275e-09</v>
+        <v>4.927298282063363e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.921602399494883e-09</v>
+        <v>4.92160239949489e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65815742223826e-09</v>
+        <v>3.658157422238221e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.015166466711044e-09</v>
+        <v>4.015166466710908e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.927654923348655e-09</v>
+        <v>3.927654923348694e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.951999197636726e-09</v>
+        <v>2.951999197636688e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.139404053463898e-09</v>
+        <v>4.139404053463987e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.427736271712305e-09</v>
+        <v>4.427736271712303e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>4.957605290585433e-09</v>
+        <v>4.957605290585223e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.105600610851067e-09</v>
+        <v>3.105600610851112e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.623814574294552e-09</v>
+        <v>6.623814574294501e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.250224683314443e-09</v>
+        <v>3.250224683314518e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>4.957275924007114e-09</v>
+        <v>4.957275924007091e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.696740301878815e-09</v>
+        <v>6.696740301878824e-09</v>
       </c>
     </row>
     <row r="4">
@@ -5550,82 +5550,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.144031716319173e-09</v>
+        <v>4.144031716319201e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.082347977084102e-09</v>
+        <v>4.082347977084119e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.220788382496036e-09</v>
+        <v>4.220788382496061e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>3.996143897895936e-09</v>
+        <v>3.996143897895955e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.079195773461802e-09</v>
+        <v>4.079195773461816e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>4.419789647680865e-09</v>
+        <v>4.419789647680877e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.211221067844805e-09</v>
+        <v>4.211221067844883e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.211983553448763e-09</v>
+        <v>4.211983553448789e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>4.158676153080543e-09</v>
+        <v>4.158676153080564e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.248249020644789e-09</v>
+        <v>4.248249020644772e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>4.18791202010381e-09</v>
+        <v>4.187912020103837e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.203700042524845e-09</v>
+        <v>4.203700042524866e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.175811425625659e-09</v>
+        <v>4.175811425625681e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.250259700980941e-09</v>
+        <v>4.250259700980964e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.152761613003459e-09</v>
+        <v>4.152761613003351e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.101962983987974e-09</v>
+        <v>4.101962983987996e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.307521598776393e-09</v>
+        <v>4.307521598776418e-09</v>
       </c>
       <c r="S4" t="n">
         <v>4.150768311427293e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.109088117963181e-09</v>
+        <v>4.109088117963207e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>4.148759364149666e-09</v>
+        <v>4.148759364149667e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.540315620127708e-09</v>
+        <v>3.540315620127727e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>4.70437397283599e-09</v>
+        <v>4.704373972836018e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>5.502087040121552e-09</v>
+        <v>5.502087040121438e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.72421666814896e-09</v>
+        <v>4.724216668148972e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.188958102879964e-09</v>
+        <v>4.188958102879975e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.474438839575622e-09</v>
+        <v>4.474438839575629e-09</v>
       </c>
       <c r="AB4" t="n">
         <v>4.203227285713114e-09</v>
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.638285938022629e-09</v>
+        <v>4.638285938022632e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.304006504636676e-09</v>
+        <v>5.304006504636695e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>4.858906077668706e-09</v>
+        <v>4.858906077668721e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.713955698996278e-09</v>
+        <v>4.713955698996289e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.375803552348124e-09</v>
+        <v>5.375803552348239e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.117308401694778e-09</v>
+        <v>5.117308401694737e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.213465633355754e-09</v>
+        <v>5.213465633355778e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>4.775625718992737e-09</v>
+        <v>4.775625718992841e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>4.905751323491198e-09</v>
+        <v>4.905751323491323e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>4.873854393548365e-09</v>
+        <v>4.873854393548221e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.518239338254083e-09</v>
+        <v>4.518239338254137e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>4.95103446499132e-09</v>
+        <v>4.951034464991387e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.331074673895913e-09</v>
+        <v>4.331074673895963e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.249259208118031e-09</v>
+        <v>5.249259208118107e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.574225249691962e-09</v>
+        <v>4.57422524969191e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.856572926412895e-09</v>
+        <v>5.8565729264129e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.626939025843208e-09</v>
+        <v>4.626939025843255e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.24913915786793e-09</v>
+        <v>5.249139157867997e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>5.876052053789242e-09</v>
+        <v>5.876052053789243e-09</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.226878485472249e-09</v>
+        <v>1.226878485472094e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.165194746237012e-09</v>
+        <v>1.16519474623701e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.303635151649099e-09</v>
+        <v>1.303635151648954e-09</v>
       </c>
       <c r="E6" t="n">
         <v>1.078990667048848e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.16204254261471e-09</v>
+        <v>1.162042542614711e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.386614068075714e-09</v>
+        <v>1.386614068075748e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.294067836997893e-09</v>
+        <v>1.294067836997775e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.294830322601837e-09</v>
+        <v>1.294830322601679e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.23144157019691e-09</v>
+        <v>1.231441570196874e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.331095789797845e-09</v>
+        <v>1.331095789797664e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.270758789256882e-09</v>
+        <v>1.270758789256725e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.286546811677753e-09</v>
+        <v>1.286546811677759e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.258658194778728e-09</v>
+        <v>1.258658194778575e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.217084121375821e-09</v>
+        <v>1.217084121375829e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.119586033398344e-09</v>
+        <v>1.119586033398216e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.184809753141034e-09</v>
+        <v>1.184809753140888e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.390368367929462e-09</v>
+        <v>1.390368367929311e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.233615080580362e-09</v>
+        <v>1.233615080580183e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.191934887116244e-09</v>
+        <v>1.191934887116099e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.115583784544543e-09</v>
+        <v>1.115583784544534e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.192436991634706e-09</v>
+        <v>1.192436991634705e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.671198393230878e-09</v>
+        <v>1.671198393230884e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.46891146051644e-09</v>
+        <v>2.468911460516306e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.807063437302031e-09</v>
+        <v>1.807063437301861e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.271804872032952e-09</v>
+        <v>1.271804872032863e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.557285608728679e-09</v>
+        <v>1.557285608728517e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.286074054866017e-09</v>
+        <v>1.28607405486601e-09</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.721132707175565e-09</v>
+        <v>1.721132707175524e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.386853273789586e-09</v>
+        <v>2.386853273789584e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>1.941752846821615e-09</v>
+        <v>1.941752846821612e-09</v>
       </c>
       <c r="F7" t="n">
         <v>1.796802468149186e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.342627972743007e-09</v>
+        <v>2.342627972743103e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.190073818811055e-09</v>
+        <v>2.190073818811048e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.296312402508661e-09</v>
+        <v>2.296312402508669e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.858472488145858e-09</v>
+        <v>1.858472488145733e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.872575743886087e-09</v>
+        <v>1.872575743886191e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.840678813943237e-09</v>
+        <v>1.840678813943087e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.601086107407061e-09</v>
+        <v>1.601086107407028e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.917858885386207e-09</v>
+        <v>1.917858885386253e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>1.983196045402938e-09</v>
+        <v>1.983196045402936e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.216083628512902e-09</v>
+        <v>2.216083628512973e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.541049670086841e-09</v>
+        <v>1.541049670086775e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.939419695565924e-09</v>
+        <v>2.939419695565791e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.709785794995984e-09</v>
+        <v>1.709785794996147e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.33198592702089e-09</v>
+        <v>2.331985927020886e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.958898822942147e-09</v>
+        <v>2.95889882294214e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.806922995353751e-09</v>
+        <v>4.80692299535423e-09</v>
       </c>
       <c r="C2" t="n">
-        <v>1.623633809308715e-09</v>
+        <v>1.623633809309105e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>3.413873810891408e-09</v>
+        <v>3.41387381089191e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>2.329492218478681e-09</v>
+        <v>2.329492218478969e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>2.285221635170925e-09</v>
+        <v>2.285221635170924e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>9.095810527587188e-09</v>
+        <v>9.095810527587718e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>2.140453829223872e-09</v>
+        <v>2.140453829224375e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.249425152917086e-09</v>
+        <v>2.249425152917545e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>6.691899156002122e-09</v>
+        <v>6.691899156002264e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>2.732753107409885e-09</v>
+        <v>2.732753107410331e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>1.047417117354212e-08</v>
+        <v>1.047417117354259e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.619910571777576e-08</v>
+        <v>1.619910571777577e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>2.946891039719659e-09</v>
+        <v>2.946891039720122e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>3.060638968295515e-09</v>
+        <v>3.060638968295871e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>5.621322214932184e-09</v>
+        <v>5.621322214932392e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.812660530309335e-09</v>
+        <v>2.812660530309817e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.35038489751849e-09</v>
+        <v>2.350384897518171e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>5.120650737331952e-09</v>
+        <v>5.120650737332436e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>2.538298798783685e-09</v>
+        <v>2.538298798784193e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>1.10379718680184e-08</v>
+        <v>1.103797186801895e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>2.687903779775786e-09</v>
+        <v>2.687903779775798e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>3.831259599632113e-09</v>
+        <v>3.83125959963274e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>6.44246974163231e-09</v>
+        <v>6.442469741632896e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.978452329565832e-09</v>
+        <v>5.978452329566296e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.973970468590368e-09</v>
+        <v>3.973970468590791e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>3.423098094109123e-09</v>
+        <v>3.423098094109577e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.117811257764422e-08</v>
+        <v>2.117811257764423e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.363814175019574e-09</v>
+        <v>3.363814175020443e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.10020880706708e-09</v>
+        <v>5.100208807067151e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.07914766128999e-09</v>
+        <v>4.079147661290233e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.598479728961255e-09</v>
+        <v>3.598479728961256e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.404596714176488e-09</v>
+        <v>5.404596714176544e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>5.02104769059543e-09</v>
+        <v>5.021047690595513e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>5.047525644650412e-09</v>
+        <v>5.047525644650421e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.743846626436306e-09</v>
+        <v>3.743846626436721e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.103916754116324e-09</v>
+        <v>4.103916754116635e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>4.01565486529394e-09</v>
+        <v>4.01565486529448e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.031633627825587e-09</v>
+        <v>3.031633627825614e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.229028277005706e-09</v>
+        <v>4.229028277005547e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.509154801730409e-09</v>
+        <v>4.50915480173055e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.054436279876177e-09</v>
+        <v>5.054436279877009e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.186552057270732e-09</v>
+        <v>3.186552057271209e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.734604779747321e-09</v>
+        <v>6.734604779747458e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.332416172044582e-09</v>
+        <v>3.332416172044518e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.054104089231642e-09</v>
+        <v>5.054104089232094e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.864181882018484e-09</v>
+        <v>6.864181882018493e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.592527133310402e-09</v>
+        <v>5.592527133311128e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>4.461555694639194e-09</v>
+        <v>4.461555694639699e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>5.08477706358325e-09</v>
+        <v>5.084777063584067e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>4.641915776090357e-09</v>
+        <v>4.641915776090754e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>4.655181650315132e-09</v>
+        <v>4.655181650315301e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.155776276149419e-09</v>
+        <v>7.155776276150043e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.620630433517843e-09</v>
+        <v>4.620630433518584e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.660349201398138e-09</v>
+        <v>4.660349201398971e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>6.110588659854011e-09</v>
+        <v>6.110588659854153e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.836516565287347e-09</v>
+        <v>4.836516565288072e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.658172546072021e-09</v>
+        <v>7.658172546072789e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>9.740663283090378e-09</v>
+        <v>9.740663283090701e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.914567327079744e-09</v>
+        <v>4.914567327080454e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.956027111350012e-09</v>
+        <v>4.956027111350717e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>5.889366085688351e-09</v>
+        <v>5.889366085689031e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.865641882613956e-09</v>
+        <v>4.865641882614595e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.69714784277617e-09</v>
+        <v>4.697147842776994e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>5.706877211284317e-09</v>
+        <v>5.706877211285002e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.765640253190904e-09</v>
+        <v>4.765640253191622e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.86367127872663e-09</v>
+        <v>7.863671278727434e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.780189280070772e-09</v>
+        <v>3.780189280070745e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>5.236909282387891e-09</v>
+        <v>5.236909282388934e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>6.188664716769455e-09</v>
+        <v>6.188664716770241e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.019535818838705e-09</v>
+        <v>6.019535818839565e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.288925718327503e-09</v>
+        <v>5.288925718328369e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.088139206499148e-09</v>
+        <v>5.088139206499929e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.158786841662843e-08</v>
+        <v>1.158786841662859e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.066530914137908e-09</v>
+        <v>5.066530914138998e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.72872645731743e-09</v>
+        <v>5.728726457317744e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.279644639503571e-09</v>
+        <v>5.279644639504107e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>5.13384880444655e-09</v>
+        <v>5.133848804446694e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.810372185582189e-09</v>
+        <v>5.81037218558273e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.50158292084173e-09</v>
+        <v>5.501582920842395e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="M5" t="n">
-        <v>5.676043294900719e-09</v>
+        <v>5.676043294900869e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.205048280112998e-09</v>
+        <v>5.205048280113453e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.336289613495467e-09</v>
+        <v>5.336289613495661e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.304119191443148e-09</v>
+        <v>5.304119191443377e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.945455005346666e-09</v>
+        <v>4.945455005347252e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.381891294454978e-09</v>
+        <v>5.38189129445568e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.444013891364015e-09</v>
+        <v>4.444013891364117e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.682742819071107e-09</v>
+        <v>5.682742819071759e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>5.001920953735421e-09</v>
+        <v>5.001920953736364e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.295144507739546e-09</v>
+        <v>6.295144507739655e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.055086710747544e-09</v>
+        <v>5.055086710748444e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.682621739482e-09</v>
+        <v>5.682621739482611e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.370608760733178e-09</v>
+        <v>6.37060876073341e-09</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.315957884141055e-09</v>
+        <v>2.315957884141642e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.184986445470015e-09</v>
+        <v>1.184986445470086e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.808207814413958e-09</v>
+        <v>1.808207814414545e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.365346526921031e-09</v>
+        <v>1.365346526921247e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.378612401145771e-09</v>
+        <v>1.37861240114577e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.762441594989034e-09</v>
+        <v>3.762441594989579e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.344061184348538e-09</v>
+        <v>1.344061184349067e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.383779952228832e-09</v>
+        <v>1.383779952229372e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>2.869347039940069e-09</v>
+        <v>2.869347039940413e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.559947316118068e-09</v>
+        <v>1.559947316118547e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>4.381603296902828e-09</v>
+        <v>4.381603296903285e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>6.464094033921057e-09</v>
+        <v>6.464094033921059e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.637998077910425e-09</v>
+        <v>1.637998077910952e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.562692430189661e-09</v>
+        <v>1.562692430190217e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>2.496031404527919e-09</v>
+        <v>2.496031404528365e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58907263344458e-09</v>
+        <v>1.589072633445125e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.420578593606864e-09</v>
+        <v>1.420578593607523e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>2.430307962115007e-09</v>
+        <v>2.430307962115524e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.489071004021605e-09</v>
+        <v>1.489071004022141e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>4.470336597566293e-09</v>
+        <v>4.47033659756672e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.379942897491953e-09</v>
+        <v>1.379942897491895e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.843574601227533e-09</v>
+        <v>1.843574601228334e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.795330035609041e-09</v>
+        <v>2.795330035609641e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.742966569669403e-09</v>
+        <v>2.742966569669933e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.012356469158195e-09</v>
+        <v>2.012356469158746e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.811569957329822e-09</v>
+        <v>1.811569957330376e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>8.311299167459054e-09</v>
+        <v>8.311299167459066e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.789961664968593e-09</v>
+        <v>1.789961664969408e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.452157208148066e-09</v>
+        <v>2.452157208148154e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="E7" t="n">
-        <v>2.003075390334241e-09</v>
+        <v>2.003075390334446e-09</v>
       </c>
       <c r="F7" t="n">
-        <v>1.857279555277233e-09</v>
+        <v>1.857279555277234e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.417037504421782e-09</v>
+        <v>2.4170375044222e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.260341300927818e-09</v>
+        <v>2.260341300928081e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.399474045731388e-09</v>
+        <v>2.399474045731391e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.928479030943689e-09</v>
+        <v>1.928479030943965e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.942954932335074e-09</v>
+        <v>1.94295493233518e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.910784510282719e-09</v>
+        <v>1.910784510282758e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.668885756177334e-09</v>
+        <v>1.668885756177708e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.988556613294582e-09</v>
+        <v>1.988556613295038e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.043767508785214e-09</v>
+        <v>2.043767508785167e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.289408137910758e-09</v>
+        <v>2.289408137911241e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.608586272574992e-09</v>
+        <v>1.608586272575715e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.018575258570192e-09</v>
+        <v>3.018575258570169e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.77851746157818e-09</v>
+        <v>1.778517461578832e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.40605249031265e-09</v>
+        <v>2.406052490313135e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.09403951156384e-09</v>
+        <v>3.094039511563849e-09</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.710875923988632e-09</v>
+        <v>1.710875923988646e-09</v>
       </c>
       <c r="C2" t="n">
         <v>1.775363411931368e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>2.262307867150213e-09</v>
+        <v>2.262307867150226e-09</v>
       </c>
       <c r="E2" t="n">
-        <v>1.383002413094093e-09</v>
+        <v>1.383002413094094e-09</v>
       </c>
       <c r="F2" t="n">
-        <v>1.657431755105729e-09</v>
+        <v>1.657431755105728e-09</v>
       </c>
       <c r="G2" t="n">
-        <v>7.486142474008092e-09</v>
+        <v>7.486142474008095e-09</v>
       </c>
       <c r="H2" t="n">
-        <v>1.956762345393184e-09</v>
+        <v>1.956762345393194e-09</v>
       </c>
       <c r="I2" t="n">
-        <v>2.076983557657612e-09</v>
+        <v>2.076983557657625e-09</v>
       </c>
       <c r="J2" t="n">
-        <v>4.026706612675962e-09</v>
+        <v>4.026706612675913e-09</v>
       </c>
       <c r="K2" t="n">
-        <v>2.407833822065717e-09</v>
+        <v>2.407833822065729e-09</v>
       </c>
       <c r="L2" t="n">
-        <v>4.630281593075639e-09</v>
+        <v>4.63028159307565e-09</v>
       </c>
       <c r="M2" t="n">
-        <v>3.168623783438915e-09</v>
+        <v>3.168623783438916e-09</v>
       </c>
       <c r="N2" t="n">
-        <v>2.257944563422385e-09</v>
+        <v>2.257944563422395e-09</v>
       </c>
       <c r="O2" t="n">
-        <v>1.910752348508931e-09</v>
+        <v>1.910752348508945e-09</v>
       </c>
       <c r="P2" t="n">
-        <v>3.481899782528598e-09</v>
+        <v>3.481899782528606e-09</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.040276043106562e-09</v>
+        <v>2.040276043106575e-09</v>
       </c>
       <c r="R2" t="n">
-        <v>2.180908392105138e-09</v>
+        <v>2.180908392105151e-09</v>
       </c>
       <c r="S2" t="n">
-        <v>2.331030584632138e-09</v>
+        <v>2.331030584632152e-09</v>
       </c>
       <c r="T2" t="n">
-        <v>1.931588742954865e-09</v>
+        <v>1.931588742954868e-09</v>
       </c>
       <c r="U2" t="n">
-        <v>3.11117613228543e-09</v>
+        <v>3.111176132285445e-09</v>
       </c>
       <c r="V2" t="n">
-        <v>2.035698727641531e-09</v>
+        <v>2.03569872764153e-09</v>
       </c>
       <c r="W2" t="n">
-        <v>2.934351956552739e-09</v>
+        <v>2.934351956552751e-09</v>
       </c>
       <c r="X2" t="n">
-        <v>5.6898439600559e-09</v>
+        <v>5.689843960055913e-09</v>
       </c>
       <c r="Y2" t="n">
-        <v>9.049962407450462e-09</v>
+        <v>9.049962407450467e-09</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.158093068378085e-09</v>
+        <v>2.158093068378097e-09</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.46921073604507e-09</v>
+        <v>2.469210736045077e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.28740415220746e-08</v>
+        <v>1.287404152207459e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3.326030518135334e-09</v>
+        <v>3.326030518135348e-09</v>
       </c>
       <c r="C3" t="n">
-        <v>5.061904203892901e-09</v>
+        <v>5.061904203892904e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="E3" t="n">
-        <v>4.043442798931073e-09</v>
+        <v>4.043442798931074e-09</v>
       </c>
       <c r="F3" t="n">
-        <v>3.564371584190323e-09</v>
+        <v>3.564371584190326e-09</v>
       </c>
       <c r="G3" t="n">
-        <v>5.35844155997328e-09</v>
+        <v>5.3584415599733e-09</v>
       </c>
       <c r="H3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="I3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="J3" t="n">
-        <v>4.977440649379425e-09</v>
+        <v>4.977440649379435e-09</v>
       </c>
       <c r="K3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="L3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="M3" t="n">
-        <v>4.973194962793973e-09</v>
+        <v>4.973194962793977e-09</v>
       </c>
       <c r="N3" t="n">
-        <v>3.704504037825448e-09</v>
+        <v>3.704504037825462e-09</v>
       </c>
       <c r="O3" t="n">
-        <v>4.063097121259309e-09</v>
+        <v>4.063097121259322e-09</v>
       </c>
       <c r="P3" t="n">
-        <v>3.975197291672031e-09</v>
+        <v>3.975197291672055e-09</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.995212609295069e-09</v>
+        <v>2.995212609295088e-09</v>
       </c>
       <c r="R3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="S3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="T3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="U3" t="n">
-        <v>4.187750195789664e-09</v>
+        <v>4.187750195789676e-09</v>
       </c>
       <c r="V3" t="n">
-        <v>4.472616531217212e-09</v>
+        <v>4.472616531217215e-09</v>
       </c>
       <c r="W3" t="n">
-        <v>5.009717519352224e-09</v>
+        <v>5.009717519352244e-09</v>
       </c>
       <c r="X3" t="n">
-        <v>3.149495547603839e-09</v>
+        <v>3.149495547603853e-09</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.683087495978176e-09</v>
+        <v>6.683087495978192e-09</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.294761312958449e-09</v>
+        <v>3.294761312958466e-09</v>
       </c>
       <c r="AA3" t="n">
-        <v>5.009386691385888e-09</v>
+        <v>5.009386691385903e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>6.790165732176689e-09</v>
+        <v>6.790165732176702e-09</v>
       </c>
     </row>
     <row r="4">
@@ -6918,13 +6918,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.305850319437639e-09</v>
+        <v>4.305850319437658e-09</v>
       </c>
       <c r="C4" t="n">
         <v>4.362730747432432e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>4.506840787479244e-09</v>
+        <v>4.506840787479259e-09</v>
       </c>
       <c r="E4" t="n">
         <v>4.142108599107886e-09</v>
@@ -6933,70 +6933,70 @@
         <v>4.271177907158569e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>6.410867160315996e-09</v>
+        <v>6.410867160316003e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>4.395473032695463e-09</v>
+        <v>4.395473032695473e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>4.439292252857101e-09</v>
+        <v>4.439292252857119e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>4.993849499709577e-09</v>
+        <v>4.99384949970961e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>4.559883289193903e-09</v>
+        <v>4.559883289193919e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>5.369939404427699e-09</v>
+        <v>5.369939404427717e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>4.814182027962791e-09</v>
+        <v>4.814182027962789e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>4.505250414506949e-09</v>
+        <v>4.505250414506968e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>4.378702929107817e-09</v>
+        <v>4.378702929107834e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>4.951367719463349e-09</v>
+        <v>4.951367719463365e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.425912794844642e-09</v>
+        <v>4.425912794844659e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>4.477171634666207e-09</v>
+        <v>4.477171634666222e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>4.531889411018514e-09</v>
+        <v>4.53188941101853e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>4.386297550210055e-09</v>
+        <v>4.386297550210071e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>4.816243302206601e-09</v>
+        <v>4.816243302206621e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>3.469551715729478e-09</v>
+        <v>3.469551715729714e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>4.751792966526339e-09</v>
+        <v>4.751792966526353e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>5.756137445182522e-09</v>
+        <v>5.756137445182536e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.980861162754953e-09</v>
+        <v>6.980861162754962e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.468855717078758e-09</v>
+        <v>4.468855717078772e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.582254453615266e-09</v>
+        <v>4.582254453615282e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.388911245629784e-09</v>
+        <v>8.38891124562978e-09</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.894555202901323e-09</v>
+        <v>4.894555202901332e-09</v>
       </c>
       <c r="C5" t="n">
-        <v>5.560636273591974e-09</v>
+        <v>5.560636273591975e-09</v>
       </c>
       <c r="D5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="E5" t="n">
-        <v>5.111807879277191e-09</v>
+        <v>5.111807879277193e-09</v>
       </c>
       <c r="F5" t="n">
-        <v>4.966235082441886e-09</v>
+        <v>4.966235082441891e-09</v>
       </c>
       <c r="G5" t="n">
-        <v>5.635345161875864e-09</v>
+        <v>5.635345161875876e-09</v>
       </c>
       <c r="H5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="I5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="J5" t="n">
-        <v>5.340380892005291e-09</v>
+        <v>5.34038089200534e-09</v>
       </c>
       <c r="K5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="L5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="M5" t="n">
         <v>5.471927032493066e-09</v>
       </c>
       <c r="N5" t="n">
-        <v>5.032504356567922e-09</v>
+        <v>5.032504356567929e-09</v>
       </c>
       <c r="O5" t="n">
-        <v>5.163207324666983e-09</v>
+        <v>5.163207324666993e-09</v>
       </c>
       <c r="P5" t="n">
-        <v>5.131168868954329e-09</v>
+        <v>5.131168868954346e-09</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.773975959789056e-09</v>
+        <v>4.77397595978907e-09</v>
       </c>
       <c r="R5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="S5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="T5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="U5" t="n">
-        <v>5.208641906582983e-09</v>
+        <v>5.208641906582996e-09</v>
       </c>
       <c r="V5" t="n">
-        <v>4.357779639399226e-09</v>
+        <v>4.357779639399442e-09</v>
       </c>
       <c r="W5" t="n">
-        <v>5.508239343993914e-09</v>
+        <v>5.508239343993932e-09</v>
       </c>
       <c r="X5" t="n">
-        <v>4.830210279120865e-09</v>
+        <v>4.830210279120882e-09</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.118163050771743e-09</v>
+        <v>6.118163050771755e-09</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.883157944795885e-09</v>
+        <v>4.883157944795902e-09</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.508118761084971e-09</v>
+        <v>5.508118761084981e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.171409960688393e-09</v>
+        <v>6.171409960688402e-09</v>
       </c>
     </row>
     <row r="6">
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.169968694752356e-09</v>
+        <v>1.169968694752369e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.226849122747146e-09</v>
+        <v>1.226849122747145e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.370959162793957e-09</v>
+        <v>1.370959162793968e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.006226974422599e-09</v>
+        <v>1.0062269744226e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.135296282473284e-09</v>
+        <v>1.135296282473283e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>3.158659620072611e-09</v>
+        <v>3.158659620072622e-09</v>
       </c>
       <c r="H6" t="n">
-        <v>1.259591408010183e-09</v>
+        <v>1.25959140801019e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.303410628171818e-09</v>
+        <v>1.303410628171829e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.881530995897143e-09</v>
+        <v>1.881530995897148e-09</v>
       </c>
       <c r="K6" t="n">
-        <v>1.42400166450862e-09</v>
+        <v>1.424001664508631e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>2.234057779742412e-09</v>
+        <v>2.234057779742425e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.678300403277503e-09</v>
+        <v>1.678300403277504e-09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.369368789821666e-09</v>
+        <v>1.369368789821681e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.126495388864434e-09</v>
+        <v>1.126495388864449e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.699160179219965e-09</v>
+        <v>1.699160179219977e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.29003117015936e-09</v>
+        <v>1.290031170159369e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.341290009980923e-09</v>
+        <v>1.341290009980933e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.396007786333229e-09</v>
+        <v>1.39600778633324e-09</v>
       </c>
       <c r="T6" t="n">
-        <v>1.250415925524772e-09</v>
+        <v>1.250415925524789e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.564035761963216e-09</v>
+        <v>1.564035761963234e-09</v>
       </c>
       <c r="V6" t="n">
         <v>1.129083264287589e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.499585426282955e-09</v>
+        <v>1.499585426282968e-09</v>
       </c>
       <c r="X6" t="n">
-        <v>2.503929904939136e-09</v>
+        <v>2.503929904939148e-09</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.844979538069671e-09</v>
+        <v>3.844979538069682e-09</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33297409239347e-09</v>
+        <v>1.33297409239348e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.446372828929983e-09</v>
+        <v>1.446372828929993e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.2530296209445e-09</v>
+        <v>5.253029620944498e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7182,13 +7182,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.758673578216036e-09</v>
+        <v>1.758673578216041e-09</v>
       </c>
       <c r="C7" t="n">
-        <v>2.424754648906691e-09</v>
+        <v>2.424754648906694e-09</v>
       </c>
       <c r="D7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="E7" t="n">
         <v>1.975926254591904e-09</v>
@@ -7197,67 +7197,67 @@
         <v>1.830353457756601e-09</v>
       </c>
       <c r="G7" t="n">
-        <v>2.38313762163248e-09</v>
+        <v>2.383137621632492e-09</v>
       </c>
       <c r="H7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="I7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="J7" t="n">
-        <v>2.228062388192864e-09</v>
+        <v>2.228062388192872e-09</v>
       </c>
       <c r="K7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="L7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="M7" t="n">
-        <v>2.336045407807779e-09</v>
+        <v>2.336045407807781e-09</v>
       </c>
       <c r="N7" t="n">
-        <v>1.896622731882639e-09</v>
+        <v>1.896622731882638e-09</v>
       </c>
       <c r="O7" t="n">
-        <v>1.910999784423595e-09</v>
+        <v>1.910999784423605e-09</v>
       </c>
       <c r="P7" t="n">
-        <v>1.878961328710945e-09</v>
+        <v>1.878961328710955e-09</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.638094335103772e-09</v>
+        <v>1.638094335103779e-09</v>
       </c>
       <c r="R7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="S7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="T7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="U7" t="n">
-        <v>1.956434366339604e-09</v>
+        <v>1.956434366339614e-09</v>
       </c>
       <c r="V7" t="n">
-        <v>2.017311187957328e-09</v>
+        <v>2.01731118795733e-09</v>
       </c>
       <c r="W7" t="n">
-        <v>2.256031803750533e-09</v>
+        <v>2.256031803750547e-09</v>
       </c>
       <c r="X7" t="n">
-        <v>1.578002738877482e-09</v>
+        <v>1.578002738877499e-09</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.982281426086459e-09</v>
+        <v>2.982281426086464e-09</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.747276320110601e-09</v>
+        <v>1.747276320110614e-09</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.372237136399687e-09</v>
+        <v>2.372237136399692e-09</v>
       </c>
       <c r="AB7" t="n">
         <v>3.035528336003112e-09</v>
